--- a/Data/vision_cleaned_manual fill listed country.xlsx
+++ b/Data/vision_cleaned_manual fill listed country.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub Projects\SUPERFUNdProject\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{01C88568-B984-4FB9-9715-460FB0258906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DA5C8A-D11B-4185-9D1F-87C5D5D84B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52695" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{AAD4E826-BAEB-49EF-BDB0-04D37C65F545}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AAD4E826-BAEB-49EF-BDB0-04D37C65F545}"/>
   </bookViews>
   <sheets>
     <sheet name="vision_cleaned" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,25 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$B$1:$E$936</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">vision_cleaned!$A$1:$N$1041</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -5799,7 +5812,7 @@
         <v>-27694955.510000002</v>
       </c>
       <c r="N2">
-        <v>-0.38</v>
+        <v>-3.8E-3</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
@@ -5832,7 +5845,7 @@
         <v>4079515.22</v>
       </c>
       <c r="N3">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
@@ -5865,7 +5878,7 @@
         <v>446108.04249999998</v>
       </c>
       <c r="N4">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
@@ -5931,7 +5944,7 @@
         <v>76540348.170000002</v>
       </c>
       <c r="N6">
-        <v>1.06</v>
+        <v>1.06E-2</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
@@ -5997,7 +6010,7 @@
         <v>46840409.68</v>
       </c>
       <c r="N8">
-        <v>0.65</v>
+        <v>6.5000000000000006E-3</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
@@ -6030,7 +6043,7 @@
         <v>-2025471.676</v>
       </c>
       <c r="N9">
-        <v>-0.03</v>
+        <v>-2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
@@ -6063,7 +6076,7 @@
         <v>522578.24329999997</v>
       </c>
       <c r="N10">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
@@ -6096,7 +6109,7 @@
         <v>-3676120.7250000001</v>
       </c>
       <c r="N11">
-        <v>-0.05</v>
+        <v>-5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -6162,7 +6175,7 @@
         <v>703074.09649999999</v>
       </c>
       <c r="N13">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
@@ -6195,7 +6208,7 @@
         <v>-3343050.3020000001</v>
       </c>
       <c r="N14">
-        <v>-0.05</v>
+        <v>-5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
@@ -6261,7 +6274,7 @@
         <v>1294277.291</v>
       </c>
       <c r="N16">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
@@ -6294,7 +6307,7 @@
         <v>-1500839.9539999999</v>
       </c>
       <c r="N17">
-        <v>-0.02</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
@@ -6327,7 +6340,7 @@
         <v>-1751776.865</v>
       </c>
       <c r="N18">
-        <v>-0.02</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
@@ -6360,7 +6373,7 @@
         <v>661958.74369999999</v>
       </c>
       <c r="N19">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
@@ -6393,7 +6406,7 @@
         <v>-1280737.558</v>
       </c>
       <c r="N20">
-        <v>-0.02</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
@@ -6426,7 +6439,7 @@
         <v>-1200555.0090000001</v>
       </c>
       <c r="N21">
-        <v>-0.02</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
@@ -6459,7 +6472,7 @@
         <v>-766039.1237</v>
       </c>
       <c r="N22">
-        <v>-0.01</v>
+        <v>-1E-4</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
@@ -6492,7 +6505,7 @@
         <v>1492675.389</v>
       </c>
       <c r="N23">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
@@ -6525,7 +6538,7 @@
         <v>-30328902.550000001</v>
       </c>
       <c r="N24">
-        <v>-0.42</v>
+        <v>-4.1999999999999997E-3</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
@@ -6558,7 +6571,7 @@
         <v>-1134470.3319999999</v>
       </c>
       <c r="N25">
-        <v>-0.02</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
@@ -6690,7 +6703,7 @@
         <v>9859013.3190000001</v>
       </c>
       <c r="N29">
-        <v>0.13999999999999899</v>
+        <v>1.3999999999999898E-3</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
@@ -6723,7 +6736,7 @@
         <v>-6533076.6200000001</v>
       </c>
       <c r="N30">
-        <v>-0.09</v>
+        <v>-8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
@@ -6789,7 +6802,7 @@
         <v>3826125.5660000001</v>
       </c>
       <c r="N32">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
@@ -6822,7 +6835,7 @@
         <v>83430408.819999993</v>
       </c>
       <c r="N33">
-        <v>1.1599999999999999</v>
+        <v>1.1599999999999999E-2</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
@@ -6888,7 +6901,7 @@
         <v>569715.04350000003</v>
       </c>
       <c r="N35">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
@@ -7086,7 +7099,7 @@
         <v>1109012.666</v>
       </c>
       <c r="N41">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
@@ -7119,7 +7132,7 @@
         <v>590082.93740000005</v>
       </c>
       <c r="N42">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
@@ -7284,7 +7297,7 @@
         <v>413947.41739999998</v>
       </c>
       <c r="N47">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
@@ -7581,7 +7594,7 @@
         <v>19874074.25</v>
       </c>
       <c r="N56">
-        <v>0.27999999999999903</v>
+        <v>2.7999999999999904E-3</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
@@ -7713,7 +7726,7 @@
         <v>1947936.8289999999</v>
       </c>
       <c r="N60">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
@@ -7746,7 +7759,7 @@
         <v>5661049.7980000004</v>
       </c>
       <c r="N61">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
@@ -7779,7 +7792,7 @@
         <v>85682230.810000002</v>
       </c>
       <c r="N62">
-        <v>1.19</v>
+        <v>1.1899999999999999E-2</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
@@ -7812,7 +7825,7 @@
         <v>25026548</v>
       </c>
       <c r="N63">
-        <v>0.35</v>
+        <v>3.4999999999999996E-3</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
@@ -7878,7 +7891,7 @@
         <v>14954461.880000001</v>
       </c>
       <c r="N65">
-        <v>0.21</v>
+        <v>2.0999999999999999E-3</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
@@ -7944,7 +7957,7 @@
         <v>-2993821.5529999998</v>
       </c>
       <c r="N67">
-        <v>-0.04</v>
+        <v>-4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
@@ -7974,7 +7987,7 @@
         <v>303538343.69389999</v>
       </c>
       <c r="N68">
-        <v>4.22</v>
+        <v>4.2199999999999994E-2</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
@@ -8004,7 +8017,7 @@
         <v>11339775.289999999</v>
       </c>
       <c r="N69">
-        <v>0.16</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
@@ -8034,7 +8047,7 @@
         <v>41319805.200000003</v>
       </c>
       <c r="N70">
-        <v>0.56999999999999995</v>
+        <v>5.6999999999999993E-3</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
@@ -8064,7 +8077,7 @@
         <v>58424440.109999999</v>
       </c>
       <c r="N71">
-        <v>0.80999999999999905</v>
+        <v>8.0999999999999909E-3</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
@@ -8094,7 +8107,7 @@
         <v>34019584.340000004</v>
       </c>
       <c r="N72">
-        <v>0.47</v>
+        <v>4.6999999999999993E-3</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
@@ -8124,7 +8137,7 @@
         <v>126922848.09999999</v>
       </c>
       <c r="N73">
-        <v>1.76</v>
+        <v>1.7600000000000001E-2</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
@@ -8154,7 +8167,7 @@
         <v>70747519.340000004</v>
       </c>
       <c r="N74">
-        <v>0.98</v>
+        <v>9.7999999999999997E-3</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
@@ -8184,7 +8197,7 @@
         <v>342773972.38</v>
       </c>
       <c r="N75">
-        <v>4.75</v>
+        <v>4.7500000000000001E-2</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.35">
@@ -8214,7 +8227,7 @@
         <v>872351744.89999998</v>
       </c>
       <c r="N76">
-        <v>12.08</v>
+        <v>0.1208</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.35">
@@ -8244,7 +8257,7 @@
         <v>70867352.799999997</v>
       </c>
       <c r="N77">
-        <v>0.98</v>
+        <v>9.7999999999999997E-3</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
@@ -8274,7 +8287,7 @@
         <v>117006712.3</v>
       </c>
       <c r="N78">
-        <v>1.6199999999999899</v>
+        <v>1.6199999999999899E-2</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
@@ -8304,7 +8317,7 @@
         <v>210024351.09999999</v>
       </c>
       <c r="N79">
-        <v>2.91</v>
+        <v>2.9100000000000001E-2</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
@@ -8334,7 +8347,7 @@
         <v>95187814.280000001</v>
       </c>
       <c r="N80">
-        <v>1.32</v>
+        <v>1.32E-2</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
@@ -8364,7 +8377,7 @@
         <v>47410871.369999997</v>
       </c>
       <c r="N81">
-        <v>0.66</v>
+        <v>6.6E-3</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
@@ -8394,7 +8407,7 @@
         <v>1412848846.75</v>
       </c>
       <c r="N82">
-        <v>19.57</v>
+        <v>0.19570000000000001</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
@@ -8430,7 +8443,7 @@
         <v>570693.85419999994</v>
       </c>
       <c r="N83">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
@@ -8466,7 +8479,7 @@
         <v>2468616.5619999999</v>
       </c>
       <c r="N84">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
@@ -8502,7 +8515,7 @@
         <v>1660843.2590000001</v>
       </c>
       <c r="N85">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.35">
@@ -8538,7 +8551,7 @@
         <v>786440.09340000001</v>
       </c>
       <c r="N86">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.35">
@@ -8574,7 +8587,7 @@
         <v>3867102.4449999998</v>
       </c>
       <c r="N87">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.35">
@@ -8610,7 +8623,7 @@
         <v>7174547.2860000003</v>
       </c>
       <c r="N88">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.35">
@@ -8646,7 +8659,7 @@
         <v>10090816.75</v>
       </c>
       <c r="N89">
-        <v>0.13999999999999899</v>
+        <v>1.3999999999999898E-3</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.35">
@@ -8682,7 +8695,7 @@
         <v>1889015.2760000001</v>
       </c>
       <c r="N90">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.35">
@@ -8718,7 +8731,7 @@
         <v>1876816.548</v>
       </c>
       <c r="N91">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.35">
@@ -8754,7 +8767,7 @@
         <v>3340498.3790000002</v>
       </c>
       <c r="N92">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.35">
@@ -8790,7 +8803,7 @@
         <v>1176211.662</v>
       </c>
       <c r="N93">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.35">
@@ -8826,7 +8839,7 @@
         <v>5456460.1169999996</v>
       </c>
       <c r="N94">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.35">
@@ -8862,7 +8875,7 @@
         <v>5778436.1069999998</v>
       </c>
       <c r="N95">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.35">
@@ -8898,7 +8911,7 @@
         <v>926330.27249999996</v>
       </c>
       <c r="N96">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.35">
@@ -8934,7 +8947,7 @@
         <v>3754434.2170000002</v>
       </c>
       <c r="N97">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.35">
@@ -8970,7 +8983,7 @@
         <v>3497432.0019999999</v>
       </c>
       <c r="N98">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.35">
@@ -9006,7 +9019,7 @@
         <v>3997400.2650000001</v>
       </c>
       <c r="N99">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.35">
@@ -9042,7 +9055,7 @@
         <v>741742.64619999996</v>
       </c>
       <c r="N100">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.35">
@@ -9078,7 +9091,7 @@
         <v>2050695.699</v>
       </c>
       <c r="N101">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.35">
@@ -9114,7 +9127,7 @@
         <v>3587305.3459999999</v>
       </c>
       <c r="N102">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.35">
@@ -9150,7 +9163,7 @@
         <v>4628946.07</v>
       </c>
       <c r="N103">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.35">
@@ -9186,7 +9199,7 @@
         <v>424841.77490000002</v>
       </c>
       <c r="N104">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.35">
@@ -9222,7 +9235,7 @@
         <v>879778.34629999998</v>
       </c>
       <c r="N105">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.35">
@@ -9258,7 +9271,7 @@
         <v>4153109.0819999999</v>
       </c>
       <c r="N106">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.35">
@@ -9366,7 +9379,7 @@
         <v>439785.3529</v>
       </c>
       <c r="N109">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.35">
@@ -9402,7 +9415,7 @@
         <v>1907465.182</v>
       </c>
       <c r="N110">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.35">
@@ -9438,7 +9451,7 @@
         <v>5691254.2130000005</v>
       </c>
       <c r="N111">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.35">
@@ -9510,7 +9523,7 @@
         <v>3515308.3689999999</v>
       </c>
       <c r="N113">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.35">
@@ -9546,7 +9559,7 @@
         <v>25885995.149999999</v>
       </c>
       <c r="N114">
-        <v>0.36</v>
+        <v>3.5999999999999999E-3</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.35">
@@ -9582,7 +9595,7 @@
         <v>48209806.950000003</v>
       </c>
       <c r="N115">
-        <v>0.67</v>
+        <v>6.7000000000000002E-3</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.35">
@@ -9618,7 +9631,7 @@
         <v>2776144.0460000001</v>
       </c>
       <c r="N116">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.35">
@@ -9654,7 +9667,7 @@
         <v>2222920.6359999999</v>
       </c>
       <c r="N117">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.35">
@@ -9690,7 +9703,7 @@
         <v>68328759.280000001</v>
       </c>
       <c r="N118">
-        <v>0.95</v>
+        <v>9.4999999999999998E-3</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.35">
@@ -9726,7 +9739,7 @@
         <v>3654739.3480000002</v>
       </c>
       <c r="N119">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.35">
@@ -9762,7 +9775,7 @@
         <v>2654841.4879999999</v>
       </c>
       <c r="N120">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.35">
@@ -9798,7 +9811,7 @@
         <v>764228.71360000002</v>
       </c>
       <c r="N121">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.35">
@@ -9834,7 +9847,7 @@
         <v>1229681.49</v>
       </c>
       <c r="N122">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.35">
@@ -9870,7 +9883,7 @@
         <v>571363.66740000003</v>
       </c>
       <c r="N123">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.35">
@@ -9906,7 +9919,7 @@
         <v>4049679.517</v>
       </c>
       <c r="N124">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.35">
@@ -9942,7 +9955,7 @@
         <v>4197577.2659999998</v>
       </c>
       <c r="N125">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.35">
@@ -9978,7 +9991,7 @@
         <v>8054453.9989999998</v>
       </c>
       <c r="N126">
-        <v>0.11</v>
+        <v>1.1000000000000001E-3</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.35">
@@ -10014,7 +10027,7 @@
         <v>1827630.997</v>
       </c>
       <c r="N127">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.35">
@@ -10086,7 +10099,7 @@
         <v>20062075.73</v>
       </c>
       <c r="N129">
-        <v>0.27999999999999903</v>
+        <v>2.7999999999999904E-3</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.35">
@@ -10122,7 +10135,7 @@
         <v>3833509.11</v>
       </c>
       <c r="N130">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.35">
@@ -10158,7 +10171,7 @@
         <v>1928805.267</v>
       </c>
       <c r="N131">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.35">
@@ -10194,7 +10207,7 @@
         <v>3483837.0520000001</v>
       </c>
       <c r="N132">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.35">
@@ -10230,7 +10243,7 @@
         <v>41274318.82</v>
       </c>
       <c r="N133">
-        <v>0.56999999999999995</v>
+        <v>5.6999999999999993E-3</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.35">
@@ -10266,7 +10279,7 @@
         <v>797214.42989999999</v>
       </c>
       <c r="N134">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.35">
@@ -10302,7 +10315,7 @@
         <v>3241526.3659999999</v>
       </c>
       <c r="N135">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.35">
@@ -10338,7 +10351,7 @@
         <v>1025393.61</v>
       </c>
       <c r="N136">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.35">
@@ -10374,7 +10387,7 @@
         <v>98454125.5</v>
       </c>
       <c r="N137">
-        <v>1.3599999999999901</v>
+        <v>1.35999999999999E-2</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.35">
@@ -10410,7 +10423,7 @@
         <v>5000377.3130000001</v>
       </c>
       <c r="N138">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.35">
@@ -10446,7 +10459,7 @@
         <v>3172836.9819999998</v>
       </c>
       <c r="N139">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.35">
@@ -10482,7 +10495,7 @@
         <v>1230079.7520000001</v>
       </c>
       <c r="N140">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.35">
@@ -10518,7 +10531,7 @@
         <v>1632080.406</v>
       </c>
       <c r="N141">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.35">
@@ -10554,7 +10567,7 @@
         <v>443717.55379999999</v>
       </c>
       <c r="N142">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.35">
@@ -10590,7 +10603,7 @@
         <v>44949411.979999997</v>
       </c>
       <c r="N143">
-        <v>0.62</v>
+        <v>6.1999999999999998E-3</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.35">
@@ -10626,7 +10639,7 @@
         <v>2641106.8820000002</v>
       </c>
       <c r="N144">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.35">
@@ -10662,7 +10675,7 @@
         <v>671923.20160000003</v>
       </c>
       <c r="N145">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.35">
@@ -10698,7 +10711,7 @@
         <v>1234188.6499999999</v>
       </c>
       <c r="N146">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.35">
@@ -10734,7 +10747,7 @@
         <v>7749752.585</v>
       </c>
       <c r="N147">
-        <v>0.11</v>
+        <v>1.1000000000000001E-3</v>
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.35">
@@ -10770,7 +10783,7 @@
         <v>2241328.7549999999</v>
       </c>
       <c r="N148">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.35">
@@ -10806,7 +10819,7 @@
         <v>1794096.5009999999</v>
       </c>
       <c r="N149">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.35">
@@ -10842,7 +10855,7 @@
         <v>4363935.426</v>
       </c>
       <c r="N150">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.35">
@@ -10878,7 +10891,7 @@
         <v>2951692.1570000001</v>
       </c>
       <c r="N151">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.35">
@@ -10914,7 +10927,7 @@
         <v>1274529.3259999999</v>
       </c>
       <c r="N152">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.35">
@@ -10950,7 +10963,7 @@
         <v>5206144.3320000004</v>
       </c>
       <c r="N153">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.35">
@@ -10986,7 +10999,7 @@
         <v>5834958.4550000001</v>
       </c>
       <c r="N154">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.35">
@@ -11022,7 +11035,7 @@
         <v>5192245.0120000001</v>
       </c>
       <c r="N155">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.35">
@@ -11058,7 +11071,7 @@
         <v>679111.47739999997</v>
       </c>
       <c r="N156">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.35">
@@ -11094,7 +11107,7 @@
         <v>4152895.77</v>
       </c>
       <c r="N157">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.35">
@@ -11130,7 +11143,7 @@
         <v>394549.93489999999</v>
       </c>
       <c r="N158">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.35">
@@ -11166,7 +11179,7 @@
         <v>635527.28009999997</v>
       </c>
       <c r="N159">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.35">
@@ -11238,7 +11251,7 @@
         <v>1259898.602</v>
       </c>
       <c r="N161">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.35">
@@ -11310,7 +11323,7 @@
         <v>1723761.128</v>
       </c>
       <c r="N163">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.35">
@@ -11346,7 +11359,7 @@
         <v>975097.19140000001</v>
       </c>
       <c r="N164">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.35">
@@ -11418,7 +11431,7 @@
         <v>5573663.5350000001</v>
       </c>
       <c r="N166">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.35">
@@ -11454,7 +11467,7 @@
         <v>374679.39500000002</v>
       </c>
       <c r="N167">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.35">
@@ -11490,7 +11503,7 @@
         <v>1022507.915</v>
       </c>
       <c r="N168">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.35">
@@ -11526,7 +11539,7 @@
         <v>1990862.4439999999</v>
       </c>
       <c r="N169">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.35">
@@ -11562,7 +11575,7 @@
         <v>2823293.0759999999</v>
       </c>
       <c r="N170">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.35">
@@ -11598,7 +11611,7 @@
         <v>4054544.148</v>
       </c>
       <c r="N171">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.35">
@@ -11634,7 +11647,7 @@
         <v>557031.96019999997</v>
       </c>
       <c r="N172">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.35">
@@ -11670,7 +11683,7 @@
         <v>3374525.94</v>
       </c>
       <c r="N173">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.35">
@@ -11742,7 +11755,7 @@
         <v>4385869.5020000003</v>
       </c>
       <c r="N175">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.35">
@@ -11778,7 +11791,7 @@
         <v>3817573.9070000001</v>
       </c>
       <c r="N176">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.35">
@@ -11814,7 +11827,7 @@
         <v>644964.30850000004</v>
       </c>
       <c r="N177">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.35">
@@ -11850,7 +11863,7 @@
         <v>585898.30660000001</v>
       </c>
       <c r="N178">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.35">
@@ -11886,7 +11899,7 @@
         <v>1757000.463</v>
       </c>
       <c r="N179">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.35">
@@ -11922,7 +11935,7 @@
         <v>2356093.0520000001</v>
       </c>
       <c r="N180">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.35">
@@ -11958,7 +11971,7 @@
         <v>3440508.9840000002</v>
       </c>
       <c r="N181">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.35">
@@ -11994,7 +12007,7 @@
         <v>1044219.437</v>
       </c>
       <c r="N182">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.35">
@@ -12030,7 +12043,7 @@
         <v>12878251.800000001</v>
       </c>
       <c r="N183">
-        <v>0.18</v>
+        <v>1.8E-3</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.35">
@@ -12066,7 +12079,7 @@
         <v>825812.01100000006</v>
       </c>
       <c r="N184">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.35">
@@ -12102,7 +12115,7 @@
         <v>2462517.4479999999</v>
       </c>
       <c r="N185">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.35">
@@ -12138,7 +12151,7 @@
         <v>361201.4621</v>
       </c>
       <c r="N186">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.35">
@@ -12174,7 +12187,7 @@
         <v>920819.33360000001</v>
       </c>
       <c r="N187">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.35">
@@ -12210,7 +12223,7 @@
         <v>1080324.06</v>
       </c>
       <c r="N188">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.35">
@@ -12246,7 +12259,7 @@
         <v>4013222.5159999998</v>
       </c>
       <c r="N189">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.35">
@@ -12282,7 +12295,7 @@
         <v>4935251.5290000001</v>
       </c>
       <c r="N190">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.35">
@@ -12318,7 +12331,7 @@
         <v>601595.75179999997</v>
       </c>
       <c r="N191">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.35">
@@ -12354,7 +12367,7 @@
         <v>976609.98829999997</v>
       </c>
       <c r="N192">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.35">
@@ -12390,7 +12403,7 @@
         <v>2102335.9980000001</v>
       </c>
       <c r="N193">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.35">
@@ -12426,7 +12439,7 @@
         <v>1658411.1869999999</v>
       </c>
       <c r="N194">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.35">
@@ -12462,7 +12475,7 @@
         <v>670804.10600000003</v>
       </c>
       <c r="N195">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.35">
@@ -12498,7 +12511,7 @@
         <v>3690696.7919999999</v>
       </c>
       <c r="N196">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.35">
@@ -12534,7 +12547,7 @@
         <v>10556732.119999999</v>
       </c>
       <c r="N197">
-        <v>0.15</v>
+        <v>1.5E-3</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.35">
@@ -12570,7 +12583,7 @@
         <v>2789499.6069999998</v>
       </c>
       <c r="N198">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.35">
@@ -12606,7 +12619,7 @@
         <v>1038619.664</v>
       </c>
       <c r="N199">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.35">
@@ -12642,7 +12655,7 @@
         <v>138150589.59999999</v>
       </c>
       <c r="N200">
-        <v>1.91</v>
+        <v>1.9099999999999999E-2</v>
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.35">
@@ -12678,7 +12691,7 @@
         <v>647552.45889999997</v>
       </c>
       <c r="N201">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.35">
@@ -12714,7 +12727,7 @@
         <v>2040000.53</v>
       </c>
       <c r="N202">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.35">
@@ -12750,7 +12763,7 @@
         <v>6332424.7230000002</v>
       </c>
       <c r="N203">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.35">
@@ -12786,7 +12799,7 @@
         <v>2354697.0419999999</v>
       </c>
       <c r="N204">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.35">
@@ -12858,7 +12871,7 @@
         <v>10447463.18</v>
       </c>
       <c r="N206">
-        <v>0.13999999999999899</v>
+        <v>1.3999999999999898E-3</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.35">
@@ -12894,7 +12907,7 @@
         <v>10365814.01</v>
       </c>
       <c r="N207">
-        <v>0.13999999999999899</v>
+        <v>1.3999999999999898E-3</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.35">
@@ -12930,7 +12943,7 @@
         <v>1032819.009</v>
       </c>
       <c r="N208">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.35">
@@ -12966,7 +12979,7 @@
         <v>1109508.9550000001</v>
       </c>
       <c r="N209">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.35">
@@ -13002,7 +13015,7 @@
         <v>13064822.49</v>
       </c>
       <c r="N210">
-        <v>0.18</v>
+        <v>1.8E-3</v>
       </c>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.35">
@@ -13038,7 +13051,7 @@
         <v>3285851.446</v>
       </c>
       <c r="N211">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.35">
@@ -13110,7 +13123,7 @@
         <v>5899824.966</v>
       </c>
       <c r="N213">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.35">
@@ -13146,7 +13159,7 @@
         <v>2946572.0520000001</v>
       </c>
       <c r="N214">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.35">
@@ -13182,7 +13195,7 @@
         <v>10108577.48</v>
       </c>
       <c r="N215">
-        <v>0.13999999999999899</v>
+        <v>1.3999999999999898E-3</v>
       </c>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.35">
@@ -13218,7 +13231,7 @@
         <v>818646.43550000002</v>
       </c>
       <c r="N216">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.35">
@@ -13254,7 +13267,7 @@
         <v>1865726.5220000001</v>
       </c>
       <c r="N217">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.35">
@@ -13290,7 +13303,7 @@
         <v>5631498.0769999996</v>
       </c>
       <c r="N218">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.35">
@@ -13326,7 +13339,7 @@
         <v>3103021.0830000001</v>
       </c>
       <c r="N219">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.35">
@@ -13362,7 +13375,7 @@
         <v>25822204.460000001</v>
       </c>
       <c r="N220">
-        <v>0.36</v>
+        <v>3.5999999999999999E-3</v>
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.35">
@@ -13398,7 +13411,7 @@
         <v>2241162.5350000001</v>
       </c>
       <c r="N221">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.35">
@@ -13434,7 +13447,7 @@
         <v>1169304.297</v>
       </c>
       <c r="N222">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.35">
@@ -13470,7 +13483,7 @@
         <v>639431.02630000003</v>
       </c>
       <c r="N223">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.35">
@@ -13542,7 +13555,7 @@
         <v>3670958.0040000002</v>
       </c>
       <c r="N225">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.35">
@@ -13578,7 +13591,7 @@
         <v>1775332.6540000001</v>
       </c>
       <c r="N226">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.35">
@@ -13614,7 +13627,7 @@
         <v>713608.53430000006</v>
       </c>
       <c r="N227">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.35">
@@ -13650,7 +13663,7 @@
         <v>12249953.119999999</v>
       </c>
       <c r="N228">
-        <v>0.16999999999999901</v>
+        <v>1.6999999999999901E-3</v>
       </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.35">
@@ -13686,7 +13699,7 @@
         <v>3670601.7</v>
       </c>
       <c r="N229">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.35">
@@ -13722,7 +13735,7 @@
         <v>2694517.3459999999</v>
       </c>
       <c r="N230">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.35">
@@ -13794,7 +13807,7 @@
         <v>1806567.051</v>
       </c>
       <c r="N232">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.35">
@@ -13830,7 +13843,7 @@
         <v>494602.05949999997</v>
       </c>
       <c r="N233">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.35">
@@ -13866,7 +13879,7 @@
         <v>6769387.5499999998</v>
       </c>
       <c r="N234">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.35">
@@ -13902,7 +13915,7 @@
         <v>912662.66079999995</v>
       </c>
       <c r="N235">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.35">
@@ -13974,7 +13987,7 @@
         <v>3889725.3930000002</v>
       </c>
       <c r="N237">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.35">
@@ -14010,7 +14023,7 @@
         <v>1309458.365</v>
       </c>
       <c r="N238">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.35">
@@ -14046,7 +14059,7 @@
         <v>607014.2561</v>
       </c>
       <c r="N239">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.35">
@@ -14082,7 +14095,7 @@
         <v>594361.99179999996</v>
       </c>
       <c r="N240">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.35">
@@ -14118,7 +14131,7 @@
         <v>2124960.321</v>
       </c>
       <c r="N241">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.35">
@@ -14154,7 +14167,7 @@
         <v>3321672.0649999999</v>
       </c>
       <c r="N242">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.35">
@@ -14190,7 +14203,7 @@
         <v>495426.99709999998</v>
       </c>
       <c r="N243">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.35">
@@ -14226,7 +14239,7 @@
         <v>1453481.9</v>
       </c>
       <c r="N244">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.35">
@@ -14262,7 +14275,7 @@
         <v>1589551.6370000001</v>
       </c>
       <c r="N245">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.35">
@@ -14298,7 +14311,7 @@
         <v>428947.95270000002</v>
       </c>
       <c r="N246">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.35">
@@ -14334,7 +14347,7 @@
         <v>1785100.59</v>
       </c>
       <c r="N247">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.35">
@@ -14370,7 +14383,7 @@
         <v>2905138.7379999999</v>
       </c>
       <c r="N248">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.35">
@@ -14406,7 +14419,7 @@
         <v>393918.85470000003</v>
       </c>
       <c r="N249">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.35">
@@ -14442,7 +14455,7 @@
         <v>422798.68310000002</v>
       </c>
       <c r="N250">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.35">
@@ -14478,7 +14491,7 @@
         <v>1023625.781</v>
       </c>
       <c r="N251">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.35">
@@ -14514,7 +14527,7 @@
         <v>1071623.398</v>
       </c>
       <c r="N252">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.35">
@@ -14550,7 +14563,7 @@
         <v>894131.05350000004</v>
       </c>
       <c r="N253">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.35">
@@ -14586,7 +14599,7 @@
         <v>386743.16379999998</v>
       </c>
       <c r="N254">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.35">
@@ -14622,7 +14635,7 @@
         <v>985118.53020000004</v>
       </c>
       <c r="N255">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.35">
@@ -14658,7 +14671,7 @@
         <v>2302594.9180000001</v>
       </c>
       <c r="N256">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.35">
@@ -14694,7 +14707,7 @@
         <v>1960270.267</v>
       </c>
       <c r="N257">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.35">
@@ -14766,7 +14779,7 @@
         <v>1826903.1810000001</v>
       </c>
       <c r="N259">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.35">
@@ -14802,7 +14815,7 @@
         <v>795468.55310000002</v>
       </c>
       <c r="N260">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.35">
@@ -14838,7 +14851,7 @@
         <v>1685600.0919999999</v>
       </c>
       <c r="N261">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.35">
@@ -14907,7 +14920,7 @@
         <v>1318911.8959999999</v>
       </c>
       <c r="N263">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.35">
@@ -14979,7 +14992,7 @@
         <v>1988897.037</v>
       </c>
       <c r="N265">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.35">
@@ -15015,7 +15028,7 @@
         <v>11658922.539999999</v>
       </c>
       <c r="N266">
-        <v>0.16</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.35">
@@ -15051,7 +15064,7 @@
         <v>1627656.703</v>
       </c>
       <c r="N267">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.35">
@@ -15087,7 +15100,7 @@
         <v>3327522.8670000001</v>
       </c>
       <c r="N268">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.35">
@@ -15123,7 +15136,7 @@
         <v>4099902.6869999999</v>
       </c>
       <c r="N269">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.35">
@@ -15195,7 +15208,7 @@
         <v>5739349.057</v>
       </c>
       <c r="N271">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.35">
@@ -15231,7 +15244,7 @@
         <v>9565219.2750000004</v>
       </c>
       <c r="N272">
-        <v>0.13</v>
+        <v>1.2999999999999999E-3</v>
       </c>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.35">
@@ -15267,7 +15280,7 @@
         <v>3286960.9580000001</v>
       </c>
       <c r="N273">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.35">
@@ -15303,7 +15316,7 @@
         <v>994684.69880000001</v>
       </c>
       <c r="N274">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.35">
@@ -15339,7 +15352,7 @@
         <v>3933248.4210000001</v>
       </c>
       <c r="N275">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.35">
@@ -15375,7 +15388,7 @@
         <v>1390554.0330000001</v>
       </c>
       <c r="N276">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.35">
@@ -15411,7 +15424,7 @@
         <v>4674037.199</v>
       </c>
       <c r="N277">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.35">
@@ -15447,7 +15460,7 @@
         <v>4891662.2549999999</v>
       </c>
       <c r="N278">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.35">
@@ -15483,7 +15496,7 @@
         <v>982259.96790000005</v>
       </c>
       <c r="N279">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.35">
@@ -15519,7 +15532,7 @@
         <v>3247373.0750000002</v>
       </c>
       <c r="N280">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.35">
@@ -15591,7 +15604,7 @@
         <v>712724.8763</v>
       </c>
       <c r="N282">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.35">
@@ -15627,7 +15640,7 @@
         <v>2887523.0359999998</v>
       </c>
       <c r="N283">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.35">
@@ -15663,7 +15676,7 @@
         <v>13349458.77</v>
       </c>
       <c r="N284">
-        <v>0.18</v>
+        <v>1.8E-3</v>
       </c>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.35">
@@ -15699,7 +15712,7 @@
         <v>2218394.003</v>
       </c>
       <c r="N285">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.35">
@@ -15735,7 +15748,7 @@
         <v>9756619.3719999995</v>
       </c>
       <c r="N286">
-        <v>0.13999999999999899</v>
+        <v>1.3999999999999898E-3</v>
       </c>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.35">
@@ -15771,7 +15784,7 @@
         <v>4533999.3449999997</v>
       </c>
       <c r="N287">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.35">
@@ -15807,7 +15820,7 @@
         <v>892968.07479999994</v>
       </c>
       <c r="N288">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.35">
@@ -15879,7 +15892,7 @@
         <v>481642.3088</v>
       </c>
       <c r="N290">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.35">
@@ -15915,7 +15928,7 @@
         <v>2584463.423</v>
       </c>
       <c r="N291">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.35">
@@ -15951,7 +15964,7 @@
         <v>134693924.40000001</v>
       </c>
       <c r="N292">
-        <v>1.8599999999999901</v>
+        <v>1.8599999999999901E-2</v>
       </c>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.35">
@@ -15987,7 +16000,7 @@
         <v>6384433.4129999997</v>
       </c>
       <c r="N293">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.35">
@@ -16023,7 +16036,7 @@
         <v>7257800.0580000002</v>
       </c>
       <c r="N294">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.35">
@@ -16095,7 +16108,7 @@
         <v>2412801.9019999998</v>
       </c>
       <c r="N296">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.35">
@@ -16131,7 +16144,7 @@
         <v>3985757.2450000001</v>
       </c>
       <c r="N297">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.35">
@@ -16167,7 +16180,7 @@
         <v>2282837.0019999999</v>
       </c>
       <c r="N298">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.35">
@@ -16203,7 +16216,7 @@
         <v>2956911.5</v>
       </c>
       <c r="N299">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.35">
@@ -16239,7 +16252,7 @@
         <v>856922.62349999999</v>
       </c>
       <c r="N300">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.35">
@@ -16275,7 +16288,7 @@
         <v>10520580.1</v>
       </c>
       <c r="N301">
-        <v>0.15</v>
+        <v>1.5E-3</v>
       </c>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.35">
@@ -16311,7 +16324,7 @@
         <v>5507471.2130000005</v>
       </c>
       <c r="N302">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.35">
@@ -16347,7 +16360,7 @@
         <v>818762.5662</v>
       </c>
       <c r="N303">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.35">
@@ -16383,7 +16396,7 @@
         <v>875331.15179999999</v>
       </c>
       <c r="N304">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.35">
@@ -16419,7 +16432,7 @@
         <v>380291.48570000002</v>
       </c>
       <c r="N305">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.35">
@@ -16455,7 +16468,7 @@
         <v>1012701.483</v>
       </c>
       <c r="N306">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.35">
@@ -16491,7 +16504,7 @@
         <v>105770336.7</v>
       </c>
       <c r="N307">
-        <v>1.46</v>
+        <v>1.46E-2</v>
       </c>
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.35">
@@ -16527,7 +16540,7 @@
         <v>1721404.851</v>
       </c>
       <c r="N308">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.35">
@@ -16563,7 +16576,7 @@
         <v>4000183.0090000001</v>
       </c>
       <c r="N309">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.35">
@@ -16599,7 +16612,7 @@
         <v>2490154.6310000001</v>
       </c>
       <c r="N310">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.35">
@@ -16635,7 +16648,7 @@
         <v>5047527.0590000004</v>
       </c>
       <c r="N311">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.35">
@@ -16671,7 +16684,7 @@
         <v>3086886.3569999998</v>
       </c>
       <c r="N312">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.35">
@@ -16707,7 +16720,7 @@
         <v>3437888.1680000001</v>
       </c>
       <c r="N313">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.35">
@@ -16743,7 +16756,7 @@
         <v>438479.94679999998</v>
       </c>
       <c r="N314">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.35">
@@ -16815,7 +16828,7 @@
         <v>502893.21250000002</v>
       </c>
       <c r="N316">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.35">
@@ -16851,7 +16864,7 @@
         <v>860874.44889999996</v>
       </c>
       <c r="N317">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.35">
@@ -16887,7 +16900,7 @@
         <v>4482728.9419999998</v>
       </c>
       <c r="N318">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.35">
@@ -16923,7 +16936,7 @@
         <v>1635339.4380000001</v>
       </c>
       <c r="N319">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.35">
@@ -16959,7 +16972,7 @@
         <v>897281.61609999998</v>
       </c>
       <c r="N320">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.35">
@@ -16995,7 +17008,7 @@
         <v>7043746.8109999998</v>
       </c>
       <c r="N321">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.35">
@@ -17031,7 +17044,7 @@
         <v>3651686.11</v>
       </c>
       <c r="N322">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.35">
@@ -17067,7 +17080,7 @@
         <v>1906529.463</v>
       </c>
       <c r="N323">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.35">
@@ -17103,7 +17116,7 @@
         <v>6106915.2460000003</v>
       </c>
       <c r="N324">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.35">
@@ -17139,7 +17152,7 @@
         <v>1989440.5090000001</v>
       </c>
       <c r="N325">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.35">
@@ -17175,7 +17188,7 @@
         <v>776064.67590000003</v>
       </c>
       <c r="N326">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.35">
@@ -17211,7 +17224,7 @@
         <v>2618455.7349999999</v>
       </c>
       <c r="N327">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.35">
@@ -17247,7 +17260,7 @@
         <v>3644400.4759999998</v>
       </c>
       <c r="N328">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.35">
@@ -17283,7 +17296,7 @@
         <v>2503228.0460000001</v>
       </c>
       <c r="N329">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.35">
@@ -17319,7 +17332,7 @@
         <v>5189654.6119999997</v>
       </c>
       <c r="N330">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.35">
@@ -17355,7 +17368,7 @@
         <v>2255574.5950000002</v>
       </c>
       <c r="N331">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.35">
@@ -17391,7 +17404,7 @@
         <v>1298304.5490000001</v>
       </c>
       <c r="N332">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.35">
@@ -17427,7 +17440,7 @@
         <v>2902772.8879999998</v>
       </c>
       <c r="N333">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.35">
@@ -17463,7 +17476,7 @@
         <v>1869910.5660000001</v>
       </c>
       <c r="N334">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.35">
@@ -17499,7 +17512,7 @@
         <v>3168322.423</v>
       </c>
       <c r="N335">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.35">
@@ -17571,7 +17584,7 @@
         <v>1837584.52</v>
       </c>
       <c r="N337">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.35">
@@ -17607,7 +17620,7 @@
         <v>1648853.236</v>
       </c>
       <c r="N338">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.35">
@@ -17643,7 +17656,7 @@
         <v>1965281.8759999999</v>
       </c>
       <c r="N339">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.35">
@@ -17679,7 +17692,7 @@
         <v>1653327.5279999999</v>
       </c>
       <c r="N340">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.35">
@@ -17715,7 +17728,7 @@
         <v>383515.48729999998</v>
       </c>
       <c r="N341">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.35">
@@ -17787,7 +17800,7 @@
         <v>3149720.3810000001</v>
       </c>
       <c r="N343">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.35">
@@ -17823,7 +17836,7 @@
         <v>4605592.3559999997</v>
       </c>
       <c r="N344">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.35">
@@ -17859,7 +17872,7 @@
         <v>3596165.0010000002</v>
       </c>
       <c r="N345">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.35">
@@ -17895,7 +17908,7 @@
         <v>8018396.4380000001</v>
       </c>
       <c r="N346">
-        <v>0.11</v>
+        <v>1.1000000000000001E-3</v>
       </c>
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.35">
@@ -17931,7 +17944,7 @@
         <v>4249919.5860000001</v>
       </c>
       <c r="N347">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.35">
@@ -17967,7 +17980,7 @@
         <v>3482143.4589999998</v>
       </c>
       <c r="N348">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.35">
@@ -18039,7 +18052,7 @@
         <v>2335570.5649999999</v>
       </c>
       <c r="N350">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.35">
@@ -18111,7 +18124,7 @@
         <v>3197147.0819999999</v>
       </c>
       <c r="N352">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.35">
@@ -18147,7 +18160,7 @@
         <v>546580.27549999999</v>
       </c>
       <c r="N353">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.35">
@@ -18183,7 +18196,7 @@
         <v>11566343.140000001</v>
       </c>
       <c r="N354">
-        <v>0.16</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.35">
@@ -18219,7 +18232,7 @@
         <v>2454154.4900000002</v>
       </c>
       <c r="N355">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.35">
@@ -18255,7 +18268,7 @@
         <v>11728029.73</v>
       </c>
       <c r="N356">
-        <v>0.16</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.35">
@@ -18291,7 +18304,7 @@
         <v>2381041.8530000001</v>
       </c>
       <c r="N357">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.35">
@@ -18327,7 +18340,7 @@
         <v>2207725.6970000002</v>
       </c>
       <c r="N358">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.35">
@@ -18399,7 +18412,7 @@
         <v>4538760.4910000004</v>
       </c>
       <c r="N360">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.35">
@@ -18435,7 +18448,7 @@
         <v>1415121.825</v>
       </c>
       <c r="N361">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.35">
@@ -18507,7 +18520,7 @@
         <v>1176861.1170000001</v>
       </c>
       <c r="N363">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.35">
@@ -18543,7 +18556,7 @@
         <v>7340874.335</v>
       </c>
       <c r="N364">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.35">
@@ -18579,7 +18592,7 @@
         <v>3381666.8870000001</v>
       </c>
       <c r="N365">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.35">
@@ -18615,7 +18628,7 @@
         <v>3605820.5159999998</v>
       </c>
       <c r="N366">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.35">
@@ -18687,7 +18700,7 @@
         <v>1387672.429</v>
       </c>
       <c r="N368">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.35">
@@ -18723,7 +18736,7 @@
         <v>4328152.2869999995</v>
       </c>
       <c r="N369">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.35">
@@ -18795,7 +18808,7 @@
         <v>3330692.9819999998</v>
       </c>
       <c r="N371">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.35">
@@ -18831,7 +18844,7 @@
         <v>3332083.517</v>
       </c>
       <c r="N372">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.35">
@@ -18867,7 +18880,7 @@
         <v>2875449.4589999998</v>
       </c>
       <c r="N373">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.35">
@@ -18903,7 +18916,7 @@
         <v>1928170.3019999999</v>
       </c>
       <c r="N374">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.35">
@@ -18975,7 +18988,7 @@
         <v>469845.16350000002</v>
       </c>
       <c r="N376">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.35">
@@ -19011,7 +19024,7 @@
         <v>664410.21089999995</v>
       </c>
       <c r="N377">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.35">
@@ -19047,7 +19060,7 @@
         <v>3154523.4670000002</v>
       </c>
       <c r="N378">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.35">
@@ -19083,7 +19096,7 @@
         <v>2961567.5890000002</v>
       </c>
       <c r="N379">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.35">
@@ -19119,7 +19132,7 @@
         <v>790713.59030000004</v>
       </c>
       <c r="N380">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.35">
@@ -19155,7 +19168,7 @@
         <v>3560926.3059999999</v>
       </c>
       <c r="N381">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.35">
@@ -19191,7 +19204,7 @@
         <v>8119311.5489999996</v>
       </c>
       <c r="N382">
-        <v>0.11</v>
+        <v>1.1000000000000001E-3</v>
       </c>
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.35">
@@ -19227,7 +19240,7 @@
         <v>3254748.6669999999</v>
       </c>
       <c r="N383">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.35">
@@ -19263,7 +19276,7 @@
         <v>3931424.5040000002</v>
       </c>
       <c r="N384">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.35">
@@ -19335,7 +19348,7 @@
         <v>3666826.1910000001</v>
       </c>
       <c r="N386">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.35">
@@ -19371,7 +19384,7 @@
         <v>6074429.1069999998</v>
       </c>
       <c r="N387">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.35">
@@ -19407,7 +19420,7 @@
         <v>1477977.412</v>
       </c>
       <c r="N388">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="389" spans="1:14" x14ac:dyDescent="0.35">
@@ -19443,7 +19456,7 @@
         <v>1193703.8740000001</v>
       </c>
       <c r="N389">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="390" spans="1:14" x14ac:dyDescent="0.35">
@@ -19515,7 +19528,7 @@
         <v>420605.29499999998</v>
       </c>
       <c r="N391">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="392" spans="1:14" x14ac:dyDescent="0.35">
@@ -19551,7 +19564,7 @@
         <v>12425406.439999999</v>
       </c>
       <c r="N392">
-        <v>0.16999999999999901</v>
+        <v>1.6999999999999901E-3</v>
       </c>
     </row>
     <row r="393" spans="1:14" x14ac:dyDescent="0.35">
@@ -19587,7 +19600,7 @@
         <v>3208767.84</v>
       </c>
       <c r="N393">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.35">
@@ -19623,7 +19636,7 @@
         <v>501524.15549999999</v>
       </c>
       <c r="N394">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="395" spans="1:14" x14ac:dyDescent="0.35">
@@ -19659,7 +19672,7 @@
         <v>1741470.777</v>
       </c>
       <c r="N395">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="396" spans="1:14" x14ac:dyDescent="0.35">
@@ -19731,7 +19744,7 @@
         <v>3112534.5890000002</v>
       </c>
       <c r="N397">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="398" spans="1:14" x14ac:dyDescent="0.35">
@@ -19767,7 +19780,7 @@
         <v>758975.73679999996</v>
       </c>
       <c r="N398">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="399" spans="1:14" x14ac:dyDescent="0.35">
@@ -19803,7 +19816,7 @@
         <v>1117341.111</v>
       </c>
       <c r="N399">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="400" spans="1:14" x14ac:dyDescent="0.35">
@@ -19839,7 +19852,7 @@
         <v>885987.89280000003</v>
       </c>
       <c r="N400">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="401" spans="1:14" x14ac:dyDescent="0.35">
@@ -19875,7 +19888,7 @@
         <v>1905182.1580000001</v>
       </c>
       <c r="N401">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="402" spans="1:14" x14ac:dyDescent="0.35">
@@ -19911,7 +19924,7 @@
         <v>675803.14419999998</v>
       </c>
       <c r="N402">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="403" spans="1:14" x14ac:dyDescent="0.35">
@@ -19947,7 +19960,7 @@
         <v>2852079.1140000001</v>
       </c>
       <c r="N403">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="404" spans="1:14" x14ac:dyDescent="0.35">
@@ -19983,7 +19996,7 @@
         <v>3409881.2259999998</v>
       </c>
       <c r="N404">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="405" spans="1:14" x14ac:dyDescent="0.35">
@@ -20019,7 +20032,7 @@
         <v>949285.52119999996</v>
       </c>
       <c r="N405">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="406" spans="1:14" x14ac:dyDescent="0.35">
@@ -20055,7 +20068,7 @@
         <v>7141893.6670000004</v>
       </c>
       <c r="N406">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="407" spans="1:14" x14ac:dyDescent="0.35">
@@ -20091,7 +20104,7 @@
         <v>359785.12170000002</v>
       </c>
       <c r="N407">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="408" spans="1:14" x14ac:dyDescent="0.35">
@@ -20127,7 +20140,7 @@
         <v>1089590.9310000001</v>
       </c>
       <c r="N408">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="409" spans="1:14" x14ac:dyDescent="0.35">
@@ -20163,7 +20176,7 @@
         <v>1260078.4839999999</v>
       </c>
       <c r="N409">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="410" spans="1:14" x14ac:dyDescent="0.35">
@@ -20199,7 +20212,7 @@
         <v>2797487.7230000002</v>
       </c>
       <c r="N410">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="411" spans="1:14" x14ac:dyDescent="0.35">
@@ -20235,7 +20248,7 @@
         <v>4028529.608</v>
       </c>
       <c r="N411">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="412" spans="1:14" x14ac:dyDescent="0.35">
@@ -20268,7 +20281,7 @@
         <v>457350.49859999999</v>
       </c>
       <c r="N412">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="413" spans="1:14" x14ac:dyDescent="0.35">
@@ -20304,7 +20317,7 @@
         <v>1199895.247</v>
       </c>
       <c r="N413">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="414" spans="1:14" x14ac:dyDescent="0.35">
@@ -20340,7 +20353,7 @@
         <v>5578994.3550000004</v>
       </c>
       <c r="N414">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="415" spans="1:14" x14ac:dyDescent="0.35">
@@ -20376,7 +20389,7 @@
         <v>3363492.943</v>
       </c>
       <c r="N415">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="416" spans="1:14" x14ac:dyDescent="0.35">
@@ -20412,7 +20425,7 @@
         <v>417196.41840000002</v>
       </c>
       <c r="N416">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="417" spans="1:14" x14ac:dyDescent="0.35">
@@ -20448,7 +20461,7 @@
         <v>2835298.46</v>
       </c>
       <c r="N417">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="418" spans="1:14" x14ac:dyDescent="0.35">
@@ -20484,7 +20497,7 @@
         <v>3444606.63</v>
       </c>
       <c r="N418">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="419" spans="1:14" x14ac:dyDescent="0.35">
@@ -20520,7 +20533,7 @@
         <v>800234.63679999998</v>
       </c>
       <c r="N419">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="420" spans="1:14" x14ac:dyDescent="0.35">
@@ -20556,7 +20569,7 @@
         <v>6973102.5029999996</v>
       </c>
       <c r="N420">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="421" spans="1:14" x14ac:dyDescent="0.35">
@@ -20592,7 +20605,7 @@
         <v>1350754.0989999999</v>
       </c>
       <c r="N421">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="422" spans="1:14" x14ac:dyDescent="0.35">
@@ -20628,7 +20641,7 @@
         <v>933004.68689999997</v>
       </c>
       <c r="N422">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="423" spans="1:14" x14ac:dyDescent="0.35">
@@ -20664,7 +20677,7 @@
         <v>1344680.277</v>
       </c>
       <c r="N423">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="424" spans="1:14" x14ac:dyDescent="0.35">
@@ -20736,7 +20749,7 @@
         <v>3005911.0380000002</v>
       </c>
       <c r="N425">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="426" spans="1:14" x14ac:dyDescent="0.35">
@@ -20808,7 +20821,7 @@
         <v>2149172.8459999999</v>
       </c>
       <c r="N427">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="428" spans="1:14" x14ac:dyDescent="0.35">
@@ -20844,7 +20857,7 @@
         <v>892347.48149999999</v>
       </c>
       <c r="N428">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="429" spans="1:14" x14ac:dyDescent="0.35">
@@ -20880,7 +20893,7 @@
         <v>1486158.93</v>
       </c>
       <c r="N429">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="430" spans="1:14" x14ac:dyDescent="0.35">
@@ -20916,7 +20929,7 @@
         <v>1417269.382</v>
       </c>
       <c r="N430">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="431" spans="1:14" x14ac:dyDescent="0.35">
@@ -20988,7 +21001,7 @@
         <v>469418.52889999998</v>
       </c>
       <c r="N432">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="433" spans="1:14" x14ac:dyDescent="0.35">
@@ -21024,7 +21037,7 @@
         <v>4945918.9689999996</v>
       </c>
       <c r="N433">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="434" spans="1:14" x14ac:dyDescent="0.35">
@@ -21060,7 +21073,7 @@
         <v>1072026.9099999999</v>
       </c>
       <c r="N434">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="435" spans="1:14" x14ac:dyDescent="0.35">
@@ -21096,7 +21109,7 @@
         <v>651601.49250000005</v>
       </c>
       <c r="N435">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="436" spans="1:14" x14ac:dyDescent="0.35">
@@ -21276,7 +21289,7 @@
         <v>3419689.2940000002</v>
       </c>
       <c r="N440">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="441" spans="1:14" x14ac:dyDescent="0.35">
@@ -21312,7 +21325,7 @@
         <v>16159676.050000001</v>
       </c>
       <c r="N441">
-        <v>0.22</v>
+        <v>2.2000000000000001E-3</v>
       </c>
     </row>
     <row r="442" spans="1:14" x14ac:dyDescent="0.35">
@@ -21348,7 +21361,7 @@
         <v>1794265.7309999999</v>
       </c>
       <c r="N442">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="443" spans="1:14" x14ac:dyDescent="0.35">
@@ -21384,7 +21397,7 @@
         <v>909033.08219999995</v>
       </c>
       <c r="N443">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="444" spans="1:14" x14ac:dyDescent="0.35">
@@ -21456,7 +21469,7 @@
         <v>6344077.5800000001</v>
       </c>
       <c r="N445">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="446" spans="1:14" x14ac:dyDescent="0.35">
@@ -21492,7 +21505,7 @@
         <v>1573790.6629999999</v>
       </c>
       <c r="N446">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="447" spans="1:14" x14ac:dyDescent="0.35">
@@ -21528,7 +21541,7 @@
         <v>1844042.4439999999</v>
       </c>
       <c r="N447">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="448" spans="1:14" x14ac:dyDescent="0.35">
@@ -21564,7 +21577,7 @@
         <v>3056427.6490000002</v>
       </c>
       <c r="N448">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="449" spans="1:14" x14ac:dyDescent="0.35">
@@ -21600,7 +21613,7 @@
         <v>3336365.7859999998</v>
       </c>
       <c r="N449">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="450" spans="1:14" x14ac:dyDescent="0.35">
@@ -21636,7 +21649,7 @@
         <v>592103.64020000002</v>
       </c>
       <c r="N450">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="451" spans="1:14" x14ac:dyDescent="0.35">
@@ -21672,7 +21685,7 @@
         <v>2309912.4169999999</v>
       </c>
       <c r="N451">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="452" spans="1:14" x14ac:dyDescent="0.35">
@@ -21708,7 +21721,7 @@
         <v>1151126.665</v>
       </c>
       <c r="N452">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="453" spans="1:14" x14ac:dyDescent="0.35">
@@ -21744,7 +21757,7 @@
         <v>3433717.608</v>
       </c>
       <c r="N453">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="454" spans="1:14" x14ac:dyDescent="0.35">
@@ -21816,7 +21829,7 @@
         <v>871890.08810000005</v>
       </c>
       <c r="N455">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="456" spans="1:14" x14ac:dyDescent="0.35">
@@ -21852,7 +21865,7 @@
         <v>1367610.6429999999</v>
       </c>
       <c r="N456">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="457" spans="1:14" x14ac:dyDescent="0.35">
@@ -21888,7 +21901,7 @@
         <v>5435862.4009999996</v>
       </c>
       <c r="N457">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="458" spans="1:14" x14ac:dyDescent="0.35">
@@ -21924,7 +21937,7 @@
         <v>7567942.6239999998</v>
       </c>
       <c r="N458">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="459" spans="1:14" x14ac:dyDescent="0.35">
@@ -21960,7 +21973,7 @@
         <v>2596186.8139999998</v>
       </c>
       <c r="N459">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="460" spans="1:14" x14ac:dyDescent="0.35">
@@ -21996,7 +22009,7 @@
         <v>1941228.9620000001</v>
       </c>
       <c r="N460">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="461" spans="1:14" x14ac:dyDescent="0.35">
@@ -22032,7 +22045,7 @@
         <v>2415024.3969999999</v>
       </c>
       <c r="N461">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="462" spans="1:14" x14ac:dyDescent="0.35">
@@ -22068,7 +22081,7 @@
         <v>520155.93540000002</v>
       </c>
       <c r="N462">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="463" spans="1:14" x14ac:dyDescent="0.35">
@@ -22104,7 +22117,7 @@
         <v>5074696.1900000004</v>
       </c>
       <c r="N463">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="464" spans="1:14" x14ac:dyDescent="0.35">
@@ -22140,7 +22153,7 @@
         <v>3557767.4410000001</v>
       </c>
       <c r="N464">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="465" spans="1:14" x14ac:dyDescent="0.35">
@@ -22176,7 +22189,7 @@
         <v>1360141.5460000001</v>
       </c>
       <c r="N465">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="466" spans="1:14" x14ac:dyDescent="0.35">
@@ -22212,7 +22225,7 @@
         <v>621186.88710000005</v>
       </c>
       <c r="N466">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="467" spans="1:14" x14ac:dyDescent="0.35">
@@ -22248,7 +22261,7 @@
         <v>2011735.74</v>
       </c>
       <c r="N467">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="468" spans="1:14" x14ac:dyDescent="0.35">
@@ -22284,7 +22297,7 @@
         <v>1297121.247</v>
       </c>
       <c r="N468">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="469" spans="1:14" x14ac:dyDescent="0.35">
@@ -22320,7 +22333,7 @@
         <v>1452209.422</v>
       </c>
       <c r="N469">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="470" spans="1:14" x14ac:dyDescent="0.35">
@@ -22356,7 +22369,7 @@
         <v>4927432.9890000001</v>
       </c>
       <c r="N470">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="471" spans="1:14" x14ac:dyDescent="0.35">
@@ -22392,7 +22405,7 @@
         <v>1475085.97</v>
       </c>
       <c r="N471">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="472" spans="1:14" x14ac:dyDescent="0.35">
@@ -22428,7 +22441,7 @@
         <v>2876532.6120000002</v>
       </c>
       <c r="N472">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="473" spans="1:14" x14ac:dyDescent="0.35">
@@ -22464,7 +22477,7 @@
         <v>15162214.699999999</v>
       </c>
       <c r="N473">
-        <v>0.21</v>
+        <v>2.0999999999999999E-3</v>
       </c>
     </row>
     <row r="474" spans="1:14" x14ac:dyDescent="0.35">
@@ -22500,7 +22513,7 @@
         <v>2833688.7030000002</v>
       </c>
       <c r="N474">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="475" spans="1:14" x14ac:dyDescent="0.35">
@@ -22536,7 +22549,7 @@
         <v>3007817.997</v>
       </c>
       <c r="N475">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="476" spans="1:14" x14ac:dyDescent="0.35">
@@ -22572,7 +22585,7 @@
         <v>2567566.2620000001</v>
       </c>
       <c r="N476">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="477" spans="1:14" x14ac:dyDescent="0.35">
@@ -22608,7 +22621,7 @@
         <v>626591.07299999997</v>
       </c>
       <c r="N477">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="478" spans="1:14" x14ac:dyDescent="0.35">
@@ -22644,7 +22657,7 @@
         <v>1015015.974</v>
       </c>
       <c r="N478">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="479" spans="1:14" x14ac:dyDescent="0.35">
@@ -22680,7 +22693,7 @@
         <v>2458323.301</v>
       </c>
       <c r="N479">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="480" spans="1:14" x14ac:dyDescent="0.35">
@@ -22716,7 +22729,7 @@
         <v>929731.88679999998</v>
       </c>
       <c r="N480">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="481" spans="1:14" x14ac:dyDescent="0.35">
@@ -22752,7 +22765,7 @@
         <v>831856.4878</v>
       </c>
       <c r="N481">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="482" spans="1:14" x14ac:dyDescent="0.35">
@@ -22788,7 +22801,7 @@
         <v>2864817.2</v>
       </c>
       <c r="N482">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="483" spans="1:14" x14ac:dyDescent="0.35">
@@ -22824,7 +22837,7 @@
         <v>10709126.67</v>
       </c>
       <c r="N483">
-        <v>0.15</v>
+        <v>1.5E-3</v>
       </c>
     </row>
     <row r="484" spans="1:14" x14ac:dyDescent="0.35">
@@ -22860,7 +22873,7 @@
         <v>2166054.023</v>
       </c>
       <c r="N484">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="485" spans="1:14" x14ac:dyDescent="0.35">
@@ -22896,7 +22909,7 @@
         <v>4049787.0980000002</v>
       </c>
       <c r="N485">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="486" spans="1:14" x14ac:dyDescent="0.35">
@@ -22932,7 +22945,7 @@
         <v>3429432.0890000002</v>
       </c>
       <c r="N486">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="487" spans="1:14" x14ac:dyDescent="0.35">
@@ -22968,7 +22981,7 @@
         <v>14894366.810000001</v>
       </c>
       <c r="N487">
-        <v>0.21</v>
+        <v>2.0999999999999999E-3</v>
       </c>
     </row>
     <row r="488" spans="1:14" x14ac:dyDescent="0.35">
@@ -23004,7 +23017,7 @@
         <v>634030.67810000002</v>
       </c>
       <c r="N488">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="489" spans="1:14" x14ac:dyDescent="0.35">
@@ -23076,7 +23089,7 @@
         <v>6676464.1770000001</v>
       </c>
       <c r="N490">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="491" spans="1:14" x14ac:dyDescent="0.35">
@@ -23148,7 +23161,7 @@
         <v>2956943.53</v>
       </c>
       <c r="N492">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="493" spans="1:14" x14ac:dyDescent="0.35">
@@ -23184,7 +23197,7 @@
         <v>3930012.5449999999</v>
       </c>
       <c r="N493">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="494" spans="1:14" x14ac:dyDescent="0.35">
@@ -23220,7 +23233,7 @@
         <v>6643597.7369999997</v>
       </c>
       <c r="N494">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="495" spans="1:14" x14ac:dyDescent="0.35">
@@ -23256,7 +23269,7 @@
         <v>6262581.676</v>
       </c>
       <c r="N495">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="496" spans="1:14" x14ac:dyDescent="0.35">
@@ -23292,7 +23305,7 @@
         <v>1027916.999</v>
       </c>
       <c r="N496">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="497" spans="1:14" x14ac:dyDescent="0.35">
@@ -23328,7 +23341,7 @@
         <v>461680.43839999998</v>
       </c>
       <c r="N497">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="498" spans="1:14" x14ac:dyDescent="0.35">
@@ -23364,7 +23377,7 @@
         <v>558333.20570000005</v>
       </c>
       <c r="N498">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="499" spans="1:14" x14ac:dyDescent="0.35">
@@ -23436,7 +23449,7 @@
         <v>1261361.3489999999</v>
       </c>
       <c r="N500">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="501" spans="1:14" x14ac:dyDescent="0.35">
@@ -23472,7 +23485,7 @@
         <v>1686988.66</v>
       </c>
       <c r="N501">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="502" spans="1:14" x14ac:dyDescent="0.35">
@@ -23508,7 +23521,7 @@
         <v>1764870.226</v>
       </c>
       <c r="N502">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="503" spans="1:14" x14ac:dyDescent="0.35">
@@ -23544,7 +23557,7 @@
         <v>893923.96349999995</v>
       </c>
       <c r="N503">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="504" spans="1:14" x14ac:dyDescent="0.35">
@@ -23580,7 +23593,7 @@
         <v>27829554.57</v>
       </c>
       <c r="N504">
-        <v>0.38999999999999901</v>
+        <v>3.8999999999999903E-3</v>
       </c>
     </row>
     <row r="505" spans="1:14" x14ac:dyDescent="0.35">
@@ -23616,7 +23629,7 @@
         <v>3998744.4819999998</v>
       </c>
       <c r="N505">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="506" spans="1:14" x14ac:dyDescent="0.35">
@@ -23652,7 +23665,7 @@
         <v>891805.18940000003</v>
       </c>
       <c r="N506">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="507" spans="1:14" x14ac:dyDescent="0.35">
@@ -23688,7 +23701,7 @@
         <v>359074.3383</v>
       </c>
       <c r="N507">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="508" spans="1:14" x14ac:dyDescent="0.35">
@@ -23724,7 +23737,7 @@
         <v>2169134.8280000002</v>
       </c>
       <c r="N508">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="509" spans="1:14" x14ac:dyDescent="0.35">
@@ -23760,7 +23773,7 @@
         <v>827167.38249999995</v>
       </c>
       <c r="N509">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="510" spans="1:14" x14ac:dyDescent="0.35">
@@ -23796,7 +23809,7 @@
         <v>5149753.42</v>
       </c>
       <c r="N510">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="511" spans="1:14" x14ac:dyDescent="0.35">
@@ -23832,7 +23845,7 @@
         <v>25284745.18</v>
       </c>
       <c r="N511">
-        <v>0.35</v>
+        <v>3.4999999999999996E-3</v>
       </c>
     </row>
     <row r="512" spans="1:14" x14ac:dyDescent="0.35">
@@ -23868,7 +23881,7 @@
         <v>1818544.6</v>
       </c>
       <c r="N512">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="513" spans="1:14" x14ac:dyDescent="0.35">
@@ -23904,7 +23917,7 @@
         <v>1046417.094</v>
       </c>
       <c r="N513">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="514" spans="1:14" x14ac:dyDescent="0.35">
@@ -23940,7 +23953,7 @@
         <v>943049.51529999997</v>
       </c>
       <c r="N514">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="515" spans="1:14" x14ac:dyDescent="0.35">
@@ -23976,7 +23989,7 @@
         <v>789878.96189999999</v>
       </c>
       <c r="N515">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="516" spans="1:14" x14ac:dyDescent="0.35">
@@ -24012,7 +24025,7 @@
         <v>436432.72580000001</v>
       </c>
       <c r="N516">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="517" spans="1:14" x14ac:dyDescent="0.35">
@@ -24048,7 +24061,7 @@
         <v>3346403.361</v>
       </c>
       <c r="N517">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="518" spans="1:14" x14ac:dyDescent="0.35">
@@ -24084,7 +24097,7 @@
         <v>1582138.2209999999</v>
       </c>
       <c r="N518">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="519" spans="1:14" x14ac:dyDescent="0.35">
@@ -24120,7 +24133,7 @@
         <v>3304603.4750000001</v>
       </c>
       <c r="N519">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="520" spans="1:14" x14ac:dyDescent="0.35">
@@ -24156,7 +24169,7 @@
         <v>3446889.2349999999</v>
       </c>
       <c r="N520">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="521" spans="1:14" x14ac:dyDescent="0.35">
@@ -24192,7 +24205,7 @@
         <v>1463507.264</v>
       </c>
       <c r="N521">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="522" spans="1:14" x14ac:dyDescent="0.35">
@@ -24228,7 +24241,7 @@
         <v>1427757.172</v>
       </c>
       <c r="N522">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="523" spans="1:14" x14ac:dyDescent="0.35">
@@ -24264,7 +24277,7 @@
         <v>544814.92339999997</v>
       </c>
       <c r="N523">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="524" spans="1:14" x14ac:dyDescent="0.35">
@@ -24300,7 +24313,7 @@
         <v>2761841.5380000002</v>
       </c>
       <c r="N524">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="525" spans="1:14" x14ac:dyDescent="0.35">
@@ -24336,7 +24349,7 @@
         <v>677472.89870000002</v>
       </c>
       <c r="N525">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="526" spans="1:14" x14ac:dyDescent="0.35">
@@ -24372,7 +24385,7 @@
         <v>1147308.595</v>
       </c>
       <c r="N526">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="527" spans="1:14" x14ac:dyDescent="0.35">
@@ -24408,7 +24421,7 @@
         <v>3930445.7769999998</v>
       </c>
       <c r="N527">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="528" spans="1:14" x14ac:dyDescent="0.35">
@@ -24480,7 +24493,7 @@
         <v>739677.68700000003</v>
       </c>
       <c r="N529">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="530" spans="1:14" x14ac:dyDescent="0.35">
@@ -24516,7 +24529,7 @@
         <v>3593610.36</v>
       </c>
       <c r="N530">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="531" spans="1:14" x14ac:dyDescent="0.35">
@@ -24588,7 +24601,7 @@
         <v>2949973.159</v>
       </c>
       <c r="N532">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="533" spans="1:14" x14ac:dyDescent="0.35">
@@ -24660,7 +24673,7 @@
         <v>2179711.889</v>
       </c>
       <c r="N534">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="535" spans="1:14" x14ac:dyDescent="0.35">
@@ -24696,7 +24709,7 @@
         <v>767352.56050000002</v>
       </c>
       <c r="N535">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="536" spans="1:14" x14ac:dyDescent="0.35">
@@ -24732,7 +24745,7 @@
         <v>3642174.4929999998</v>
       </c>
       <c r="N536">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="537" spans="1:14" x14ac:dyDescent="0.35">
@@ -24768,7 +24781,7 @@
         <v>1409624.716</v>
       </c>
       <c r="N537">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="538" spans="1:14" x14ac:dyDescent="0.35">
@@ -24804,7 +24817,7 @@
         <v>414333.16629999998</v>
       </c>
       <c r="N538">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="539" spans="1:14" x14ac:dyDescent="0.35">
@@ -24840,7 +24853,7 @@
         <v>1306549.1529999999</v>
       </c>
       <c r="N539">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="540" spans="1:14" x14ac:dyDescent="0.35">
@@ -24876,7 +24889,7 @@
         <v>1643886.142</v>
       </c>
       <c r="N540">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="541" spans="1:14" x14ac:dyDescent="0.35">
@@ -24912,7 +24925,7 @@
         <v>3006994.8149999999</v>
       </c>
       <c r="N541">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="542" spans="1:14" x14ac:dyDescent="0.35">
@@ -24948,7 +24961,7 @@
         <v>2366583.2230000002</v>
       </c>
       <c r="N542">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="543" spans="1:14" x14ac:dyDescent="0.35">
@@ -24984,7 +24997,7 @@
         <v>3172796.352</v>
       </c>
       <c r="N543">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="544" spans="1:14" x14ac:dyDescent="0.35">
@@ -25020,7 +25033,7 @@
         <v>766043.31579999998</v>
       </c>
       <c r="N544">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="545" spans="1:14" x14ac:dyDescent="0.35">
@@ -25056,7 +25069,7 @@
         <v>1750769.66</v>
       </c>
       <c r="N545">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="546" spans="1:14" x14ac:dyDescent="0.35">
@@ -25092,7 +25105,7 @@
         <v>2940870.6239999998</v>
       </c>
       <c r="N546">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="547" spans="1:14" x14ac:dyDescent="0.35">
@@ -25128,7 +25141,7 @@
         <v>493901.86310000002</v>
       </c>
       <c r="N547">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="548" spans="1:14" x14ac:dyDescent="0.35">
@@ -25164,7 +25177,7 @@
         <v>2471290.0630000001</v>
       </c>
       <c r="N548">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="549" spans="1:14" x14ac:dyDescent="0.35">
@@ -25236,7 +25249,7 @@
         <v>957529.59479999996</v>
       </c>
       <c r="N550">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="551" spans="1:14" x14ac:dyDescent="0.35">
@@ -25272,7 +25285,7 @@
         <v>1513952.156</v>
       </c>
       <c r="N551">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="552" spans="1:14" x14ac:dyDescent="0.35">
@@ -25344,7 +25357,7 @@
         <v>7744982.3300000001</v>
       </c>
       <c r="N553">
-        <v>0.11</v>
+        <v>1.1000000000000001E-3</v>
       </c>
     </row>
     <row r="554" spans="1:14" x14ac:dyDescent="0.35">
@@ -25380,7 +25393,7 @@
         <v>1119575.699</v>
       </c>
       <c r="N554">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="555" spans="1:14" x14ac:dyDescent="0.35">
@@ -25416,7 +25429,7 @@
         <v>1525000.1740000001</v>
       </c>
       <c r="N555">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="556" spans="1:14" x14ac:dyDescent="0.35">
@@ -25488,7 +25501,7 @@
         <v>3409340.04</v>
       </c>
       <c r="N557">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="558" spans="1:14" x14ac:dyDescent="0.35">
@@ -25524,7 +25537,7 @@
         <v>10367704.619999999</v>
       </c>
       <c r="N558">
-        <v>0.13999999999999899</v>
+        <v>1.3999999999999898E-3</v>
       </c>
     </row>
     <row r="559" spans="1:14" x14ac:dyDescent="0.35">
@@ -25560,7 +25573,7 @@
         <v>858247.37659999996</v>
       </c>
       <c r="N559">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="560" spans="1:14" x14ac:dyDescent="0.35">
@@ -25596,7 +25609,7 @@
         <v>387202.25959999999</v>
       </c>
       <c r="N560">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="561" spans="1:14" x14ac:dyDescent="0.35">
@@ -25632,7 +25645,7 @@
         <v>676921.79119999998</v>
       </c>
       <c r="N561">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="562" spans="1:14" x14ac:dyDescent="0.35">
@@ -25668,7 +25681,7 @@
         <v>1394933.057</v>
       </c>
       <c r="N562">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="563" spans="1:14" x14ac:dyDescent="0.35">
@@ -25704,7 +25717,7 @@
         <v>991500.1139</v>
       </c>
       <c r="N563">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="564" spans="1:14" x14ac:dyDescent="0.35">
@@ -25740,7 +25753,7 @@
         <v>4053506.09</v>
       </c>
       <c r="N564">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="565" spans="1:14" x14ac:dyDescent="0.35">
@@ -25776,7 +25789,7 @@
         <v>2614627.6690000002</v>
       </c>
       <c r="N565">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="566" spans="1:14" x14ac:dyDescent="0.35">
@@ -25812,7 +25825,7 @@
         <v>57873480.590000004</v>
       </c>
       <c r="N566">
-        <v>0.8</v>
+        <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="567" spans="1:14" x14ac:dyDescent="0.35">
@@ -25884,7 +25897,7 @@
         <v>4623495.0429999996</v>
       </c>
       <c r="N568">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="569" spans="1:14" x14ac:dyDescent="0.35">
@@ -25920,7 +25933,7 @@
         <v>1720087.078</v>
       </c>
       <c r="N569">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="570" spans="1:14" x14ac:dyDescent="0.35">
@@ -25956,7 +25969,7 @@
         <v>1447227.3</v>
       </c>
       <c r="N570">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="571" spans="1:14" x14ac:dyDescent="0.35">
@@ -25992,7 +26005,7 @@
         <v>913029.44169999997</v>
       </c>
       <c r="N571">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="572" spans="1:14" x14ac:dyDescent="0.35">
@@ -26028,7 +26041,7 @@
         <v>1780675.5190000001</v>
       </c>
       <c r="N572">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="573" spans="1:14" x14ac:dyDescent="0.35">
@@ -26100,7 +26113,7 @@
         <v>3593084.9730000002</v>
       </c>
       <c r="N574">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="575" spans="1:14" x14ac:dyDescent="0.35">
@@ -26136,7 +26149,7 @@
         <v>2867074.3790000002</v>
       </c>
       <c r="N575">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="576" spans="1:14" x14ac:dyDescent="0.35">
@@ -26172,7 +26185,7 @@
         <v>9284900.1109999996</v>
       </c>
       <c r="N576">
-        <v>0.13</v>
+        <v>1.2999999999999999E-3</v>
       </c>
     </row>
     <row r="577" spans="1:14" x14ac:dyDescent="0.35">
@@ -26208,7 +26221,7 @@
         <v>504808.09820000001</v>
       </c>
       <c r="N577">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="578" spans="1:14" x14ac:dyDescent="0.35">
@@ -26244,7 +26257,7 @@
         <v>566634.68729999999</v>
       </c>
       <c r="N578">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="579" spans="1:14" x14ac:dyDescent="0.35">
@@ -26280,7 +26293,7 @@
         <v>3378541.4410000001</v>
       </c>
       <c r="N579">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="580" spans="1:14" x14ac:dyDescent="0.35">
@@ -26316,7 +26329,7 @@
         <v>1623368.909</v>
       </c>
       <c r="N580">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="581" spans="1:14" x14ac:dyDescent="0.35">
@@ -26352,7 +26365,7 @@
         <v>426032.076</v>
       </c>
       <c r="N581">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="582" spans="1:14" x14ac:dyDescent="0.35">
@@ -26388,7 +26401,7 @@
         <v>1171289.6510000001</v>
       </c>
       <c r="N582">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="583" spans="1:14" x14ac:dyDescent="0.35">
@@ -26424,7 +26437,7 @@
         <v>2927693.182</v>
       </c>
       <c r="N583">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="584" spans="1:14" x14ac:dyDescent="0.35">
@@ -26460,7 +26473,7 @@
         <v>16094252.93</v>
       </c>
       <c r="N584">
-        <v>0.22</v>
+        <v>2.2000000000000001E-3</v>
       </c>
     </row>
     <row r="585" spans="1:14" x14ac:dyDescent="0.35">
@@ -26496,7 +26509,7 @@
         <v>4576912.5460000001</v>
       </c>
       <c r="N585">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="586" spans="1:14" x14ac:dyDescent="0.35">
@@ -26532,7 +26545,7 @@
         <v>5902610.3059999999</v>
       </c>
       <c r="N586">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="587" spans="1:14" x14ac:dyDescent="0.35">
@@ -26568,7 +26581,7 @@
         <v>8458136.1380000003</v>
       </c>
       <c r="N587">
-        <v>0.12</v>
+        <v>1.1999999999999999E-3</v>
       </c>
     </row>
     <row r="588" spans="1:14" x14ac:dyDescent="0.35">
@@ -26604,7 +26617,7 @@
         <v>3018616.3769999999</v>
       </c>
       <c r="N588">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="589" spans="1:14" x14ac:dyDescent="0.35">
@@ -26676,7 +26689,7 @@
         <v>435987.31959999999</v>
       </c>
       <c r="N590">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="591" spans="1:14" x14ac:dyDescent="0.35">
@@ -26712,7 +26725,7 @@
         <v>637660.79890000005</v>
       </c>
       <c r="N591">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="592" spans="1:14" x14ac:dyDescent="0.35">
@@ -26748,7 +26761,7 @@
         <v>58566208.020000003</v>
       </c>
       <c r="N592">
-        <v>0.80999999999999905</v>
+        <v>8.0999999999999909E-3</v>
       </c>
     </row>
     <row r="593" spans="1:14" x14ac:dyDescent="0.35">
@@ -26784,7 +26797,7 @@
         <v>1775961.443</v>
       </c>
       <c r="N593">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="594" spans="1:14" x14ac:dyDescent="0.35">
@@ -26856,7 +26869,7 @@
         <v>2044019.9650000001</v>
       </c>
       <c r="N595">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="596" spans="1:14" x14ac:dyDescent="0.35">
@@ -26892,7 +26905,7 @@
         <v>85179282.239999995</v>
       </c>
       <c r="N596">
-        <v>1.18</v>
+        <v>1.18E-2</v>
       </c>
     </row>
     <row r="597" spans="1:14" x14ac:dyDescent="0.35">
@@ -26964,7 +26977,7 @@
         <v>6300479.9560000002</v>
       </c>
       <c r="N598">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="599" spans="1:14" x14ac:dyDescent="0.35">
@@ -27036,7 +27049,7 @@
         <v>3422594.6379999998</v>
       </c>
       <c r="N600">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="601" spans="1:14" x14ac:dyDescent="0.35">
@@ -27072,7 +27085,7 @@
         <v>474020.23229999997</v>
       </c>
       <c r="N601">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="602" spans="1:14" x14ac:dyDescent="0.35">
@@ -27108,7 +27121,7 @@
         <v>4206000.6849999996</v>
       </c>
       <c r="N602">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="603" spans="1:14" x14ac:dyDescent="0.35">
@@ -27144,7 +27157,7 @@
         <v>1993984.517</v>
       </c>
       <c r="N603">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="604" spans="1:14" x14ac:dyDescent="0.35">
@@ -27180,7 +27193,7 @@
         <v>1080200.4350000001</v>
       </c>
       <c r="N604">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="605" spans="1:14" x14ac:dyDescent="0.35">
@@ -27216,7 +27229,7 @@
         <v>1125589.452</v>
       </c>
       <c r="N605">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="606" spans="1:14" x14ac:dyDescent="0.35">
@@ -27252,7 +27265,7 @@
         <v>395413.07130000001</v>
       </c>
       <c r="N606">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="607" spans="1:14" x14ac:dyDescent="0.35">
@@ -27288,7 +27301,7 @@
         <v>1792020.952</v>
       </c>
       <c r="N607">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="608" spans="1:14" x14ac:dyDescent="0.35">
@@ -27324,7 +27337,7 @@
         <v>3933011.102</v>
       </c>
       <c r="N608">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="609" spans="1:14" x14ac:dyDescent="0.35">
@@ -27360,7 +27373,7 @@
         <v>1161126.4099999999</v>
       </c>
       <c r="N609">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="610" spans="1:14" x14ac:dyDescent="0.35">
@@ -27396,7 +27409,7 @@
         <v>6260213.8619999997</v>
       </c>
       <c r="N610">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="611" spans="1:14" x14ac:dyDescent="0.35">
@@ -27432,7 +27445,7 @@
         <v>4190885.6540000001</v>
       </c>
       <c r="N611">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="612" spans="1:14" x14ac:dyDescent="0.35">
@@ -27468,7 +27481,7 @@
         <v>3404587.0490000001</v>
       </c>
       <c r="N612">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="613" spans="1:14" x14ac:dyDescent="0.35">
@@ -27504,7 +27517,7 @@
         <v>1414128.8060000001</v>
       </c>
       <c r="N613">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="614" spans="1:14" x14ac:dyDescent="0.35">
@@ -27540,7 +27553,7 @@
         <v>2326368.5690000001</v>
       </c>
       <c r="N614">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="615" spans="1:14" x14ac:dyDescent="0.35">
@@ -27576,7 +27589,7 @@
         <v>1171622.642</v>
       </c>
       <c r="N615">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="616" spans="1:14" x14ac:dyDescent="0.35">
@@ -27612,7 +27625,7 @@
         <v>460548.6434</v>
       </c>
       <c r="N616">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="617" spans="1:14" x14ac:dyDescent="0.35">
@@ -27648,7 +27661,7 @@
         <v>1993751.9450000001</v>
       </c>
       <c r="N617">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="618" spans="1:14" x14ac:dyDescent="0.35">
@@ -27684,7 +27697,7 @@
         <v>82777521.049999997</v>
       </c>
       <c r="N618">
-        <v>1.1499999999999999</v>
+        <v>1.15E-2</v>
       </c>
     </row>
     <row r="619" spans="1:14" x14ac:dyDescent="0.35">
@@ -27720,7 +27733,7 @@
         <v>2306490.2999999998</v>
       </c>
       <c r="N619">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="620" spans="1:14" x14ac:dyDescent="0.35">
@@ -27756,7 +27769,7 @@
         <v>7159817.6289999997</v>
       </c>
       <c r="N620">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="621" spans="1:14" x14ac:dyDescent="0.35">
@@ -27792,7 +27805,7 @@
         <v>973913.8713</v>
       </c>
       <c r="N621">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="622" spans="1:14" x14ac:dyDescent="0.35">
@@ -27828,7 +27841,7 @@
         <v>1701881.537</v>
       </c>
       <c r="N622">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="623" spans="1:14" x14ac:dyDescent="0.35">
@@ -27864,7 +27877,7 @@
         <v>503522.15139999997</v>
       </c>
       <c r="N623">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="624" spans="1:14" x14ac:dyDescent="0.35">
@@ -27900,7 +27913,7 @@
         <v>6934508.523</v>
       </c>
       <c r="N624">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="625" spans="1:14" x14ac:dyDescent="0.35">
@@ -27936,7 +27949,7 @@
         <v>3316887.12</v>
       </c>
       <c r="N625">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="626" spans="1:14" x14ac:dyDescent="0.35">
@@ -27972,7 +27985,7 @@
         <v>941667.79619999998</v>
       </c>
       <c r="N626">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="627" spans="1:14" x14ac:dyDescent="0.35">
@@ -28008,7 +28021,7 @@
         <v>15959315.5</v>
       </c>
       <c r="N627">
-        <v>0.22</v>
+        <v>2.2000000000000001E-3</v>
       </c>
     </row>
     <row r="628" spans="1:14" x14ac:dyDescent="0.35">
@@ -28044,7 +28057,7 @@
         <v>1831000.061</v>
       </c>
       <c r="N628">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="629" spans="1:14" x14ac:dyDescent="0.35">
@@ -28116,7 +28129,7 @@
         <v>3249147.4249999998</v>
       </c>
       <c r="N630">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="631" spans="1:14" x14ac:dyDescent="0.35">
@@ -28152,7 +28165,7 @@
         <v>12126232.02</v>
       </c>
       <c r="N631">
-        <v>0.16999999999999901</v>
+        <v>1.6999999999999901E-3</v>
       </c>
     </row>
     <row r="632" spans="1:14" x14ac:dyDescent="0.35">
@@ -28188,7 +28201,7 @@
         <v>1518180.977</v>
       </c>
       <c r="N632">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="633" spans="1:14" x14ac:dyDescent="0.35">
@@ -28224,7 +28237,7 @@
         <v>3376456.4070000001</v>
       </c>
       <c r="N633">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="634" spans="1:14" x14ac:dyDescent="0.35">
@@ -28296,7 +28309,7 @@
         <v>1167013.8670000001</v>
       </c>
       <c r="N635">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="636" spans="1:14" x14ac:dyDescent="0.35">
@@ -28332,7 +28345,7 @@
         <v>1065755.2080000001</v>
       </c>
       <c r="N636">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="637" spans="1:14" x14ac:dyDescent="0.35">
@@ -28368,7 +28381,7 @@
         <v>844565.30599999998</v>
       </c>
       <c r="N637">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="638" spans="1:14" x14ac:dyDescent="0.35">
@@ -28404,7 +28417,7 @@
         <v>7761373.2209999999</v>
       </c>
       <c r="N638">
-        <v>0.11</v>
+        <v>1.1000000000000001E-3</v>
       </c>
     </row>
     <row r="639" spans="1:14" x14ac:dyDescent="0.35">
@@ -28476,7 +28489,7 @@
         <v>3221967.1970000002</v>
       </c>
       <c r="N640">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="641" spans="1:14" x14ac:dyDescent="0.35">
@@ -28512,7 +28525,7 @@
         <v>570664.47250000003</v>
       </c>
       <c r="N641">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="642" spans="1:14" x14ac:dyDescent="0.35">
@@ -28548,7 +28561,7 @@
         <v>3030536.3160000001</v>
       </c>
       <c r="N642">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="643" spans="1:14" x14ac:dyDescent="0.35">
@@ -28620,7 +28633,7 @@
         <v>3361803.764</v>
       </c>
       <c r="N644">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="645" spans="1:14" x14ac:dyDescent="0.35">
@@ -28656,7 +28669,7 @@
         <v>543321.97510000004</v>
       </c>
       <c r="N645">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="646" spans="1:14" x14ac:dyDescent="0.35">
@@ -28692,7 +28705,7 @@
         <v>6306492.6100000003</v>
       </c>
       <c r="N646">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="647" spans="1:14" x14ac:dyDescent="0.35">
@@ -28728,7 +28741,7 @@
         <v>3503368.0550000002</v>
       </c>
       <c r="N647">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="648" spans="1:14" x14ac:dyDescent="0.35">
@@ -28764,7 +28777,7 @@
         <v>8238763.9610000001</v>
       </c>
       <c r="N648">
-        <v>0.11</v>
+        <v>1.1000000000000001E-3</v>
       </c>
     </row>
     <row r="649" spans="1:14" x14ac:dyDescent="0.35">
@@ -28800,7 +28813,7 @@
         <v>10982397.119999999</v>
       </c>
       <c r="N649">
-        <v>0.15</v>
+        <v>1.5E-3</v>
       </c>
     </row>
     <row r="650" spans="1:14" x14ac:dyDescent="0.35">
@@ -28836,7 +28849,7 @@
         <v>979001.28839999996</v>
       </c>
       <c r="N650">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="651" spans="1:14" x14ac:dyDescent="0.35">
@@ -28872,7 +28885,7 @@
         <v>4233330.3729999997</v>
       </c>
       <c r="N651">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="652" spans="1:14" x14ac:dyDescent="0.35">
@@ -28908,7 +28921,7 @@
         <v>2966900.9270000001</v>
       </c>
       <c r="N652">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="653" spans="1:14" x14ac:dyDescent="0.35">
@@ -28944,7 +28957,7 @@
         <v>5519202.9239999996</v>
       </c>
       <c r="N653">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="654" spans="1:14" x14ac:dyDescent="0.35">
@@ -28980,7 +28993,7 @@
         <v>1829466.308</v>
       </c>
       <c r="N654">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="655" spans="1:14" x14ac:dyDescent="0.35">
@@ -29016,7 +29029,7 @@
         <v>659112.53910000005</v>
       </c>
       <c r="N655">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="656" spans="1:14" x14ac:dyDescent="0.35">
@@ -29052,7 +29065,7 @@
         <v>82267020.230000004</v>
       </c>
       <c r="N656">
-        <v>1.1399999999999999</v>
+        <v>1.1399999999999999E-2</v>
       </c>
     </row>
     <row r="657" spans="1:14" x14ac:dyDescent="0.35">
@@ -29088,7 +29101,7 @@
         <v>1289860.912</v>
       </c>
       <c r="N657">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="658" spans="1:14" x14ac:dyDescent="0.35">
@@ -29124,7 +29137,7 @@
         <v>517962.24249999999</v>
       </c>
       <c r="N658">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="659" spans="1:14" x14ac:dyDescent="0.35">
@@ -29160,7 +29173,7 @@
         <v>465020.0331</v>
       </c>
       <c r="N659">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="660" spans="1:14" x14ac:dyDescent="0.35">
@@ -29196,7 +29209,7 @@
         <v>944449.86880000005</v>
       </c>
       <c r="N660">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="661" spans="1:14" x14ac:dyDescent="0.35">
@@ -29268,7 +29281,7 @@
         <v>2836688.1179999998</v>
       </c>
       <c r="N662">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="663" spans="1:14" x14ac:dyDescent="0.35">
@@ -29304,7 +29317,7 @@
         <v>1108125.922</v>
       </c>
       <c r="N663">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="664" spans="1:14" x14ac:dyDescent="0.35">
@@ -29340,7 +29353,7 @@
         <v>1316536.7009999999</v>
       </c>
       <c r="N664">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="665" spans="1:14" x14ac:dyDescent="0.35">
@@ -29376,7 +29389,7 @@
         <v>2866541.1269999999</v>
       </c>
       <c r="N665">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="666" spans="1:14" x14ac:dyDescent="0.35">
@@ -29412,7 +29425,7 @@
         <v>8758524.6150000002</v>
       </c>
       <c r="N666">
-        <v>0.12</v>
+        <v>1.1999999999999999E-3</v>
       </c>
     </row>
     <row r="667" spans="1:14" x14ac:dyDescent="0.35">
@@ -29448,7 +29461,7 @@
         <v>2365258.2749999999</v>
       </c>
       <c r="N667">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="668" spans="1:14" x14ac:dyDescent="0.35">
@@ -29484,7 +29497,7 @@
         <v>3519265.5469999998</v>
       </c>
       <c r="N668">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="669" spans="1:14" x14ac:dyDescent="0.35">
@@ -29520,7 +29533,7 @@
         <v>3198357.9040000001</v>
       </c>
       <c r="N669">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="670" spans="1:14" x14ac:dyDescent="0.35">
@@ -29556,7 +29569,7 @@
         <v>1063202.5049999999</v>
       </c>
       <c r="N670">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="671" spans="1:14" x14ac:dyDescent="0.35">
@@ -29592,7 +29605,7 @@
         <v>7470378.3370000003</v>
       </c>
       <c r="N671">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="672" spans="1:14" x14ac:dyDescent="0.35">
@@ -29628,7 +29641,7 @@
         <v>3280165.5690000001</v>
       </c>
       <c r="N672">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="673" spans="1:14" x14ac:dyDescent="0.35">
@@ -29664,7 +29677,7 @@
         <v>3953397.38</v>
       </c>
       <c r="N673">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="674" spans="1:14" x14ac:dyDescent="0.35">
@@ -29700,7 +29713,7 @@
         <v>2026100.5090000001</v>
       </c>
       <c r="N674">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="675" spans="1:14" x14ac:dyDescent="0.35">
@@ -29736,7 +29749,7 @@
         <v>3735202.9789999998</v>
       </c>
       <c r="N675">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="676" spans="1:14" x14ac:dyDescent="0.35">
@@ -29772,7 +29785,7 @@
         <v>556830.06259999995</v>
       </c>
       <c r="N676">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="677" spans="1:14" x14ac:dyDescent="0.35">
@@ -29844,7 +29857,7 @@
         <v>3474169.9070000001</v>
       </c>
       <c r="N678">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="679" spans="1:14" x14ac:dyDescent="0.35">
@@ -29880,7 +29893,7 @@
         <v>4226867.28</v>
       </c>
       <c r="N679">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="680" spans="1:14" x14ac:dyDescent="0.35">
@@ -29916,7 +29929,7 @@
         <v>2720309.79</v>
       </c>
       <c r="N680">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="681" spans="1:14" x14ac:dyDescent="0.35">
@@ -29952,7 +29965,7 @@
         <v>2187934.1639999999</v>
       </c>
       <c r="N681">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="682" spans="1:14" x14ac:dyDescent="0.35">
@@ -29988,7 +30001,7 @@
         <v>5433213.3629999999</v>
       </c>
       <c r="N682">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="683" spans="1:14" x14ac:dyDescent="0.35">
@@ -30024,7 +30037,7 @@
         <v>495949.15480000002</v>
       </c>
       <c r="N683">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="684" spans="1:14" x14ac:dyDescent="0.35">
@@ -30060,7 +30073,7 @@
         <v>3265758.51</v>
       </c>
       <c r="N684">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="685" spans="1:14" x14ac:dyDescent="0.35">
@@ -30096,7 +30109,7 @@
         <v>1643361.1680000001</v>
       </c>
       <c r="N685">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="686" spans="1:14" x14ac:dyDescent="0.35">
@@ -30132,7 +30145,7 @@
         <v>10429268.52</v>
       </c>
       <c r="N686">
-        <v>0.13999999999999899</v>
+        <v>1.3999999999999898E-3</v>
       </c>
     </row>
     <row r="687" spans="1:14" x14ac:dyDescent="0.35">
@@ -30168,7 +30181,7 @@
         <v>4301670.0949999997</v>
       </c>
       <c r="N687">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="688" spans="1:14" x14ac:dyDescent="0.35">
@@ -30204,7 +30217,7 @@
         <v>2608846.6510000001</v>
       </c>
       <c r="N688">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="689" spans="1:14" x14ac:dyDescent="0.35">
@@ -30240,7 +30253,7 @@
         <v>2988749.841</v>
       </c>
       <c r="N689">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="690" spans="1:14" x14ac:dyDescent="0.35">
@@ -30276,7 +30289,7 @@
         <v>1436736.791</v>
       </c>
       <c r="N690">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="691" spans="1:14" x14ac:dyDescent="0.35">
@@ -30312,7 +30325,7 @@
         <v>3228496.6239999998</v>
       </c>
       <c r="N691">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="692" spans="1:14" x14ac:dyDescent="0.35">
@@ -30348,7 +30361,7 @@
         <v>3620200.952</v>
       </c>
       <c r="N692">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="693" spans="1:14" x14ac:dyDescent="0.35">
@@ -30384,7 +30397,7 @@
         <v>3117926.6579999998</v>
       </c>
       <c r="N693">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="694" spans="1:14" x14ac:dyDescent="0.35">
@@ -30420,7 +30433,7 @@
         <v>942371.94160000002</v>
       </c>
       <c r="N694">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="695" spans="1:14" x14ac:dyDescent="0.35">
@@ -30492,7 +30505,7 @@
         <v>1108764.94</v>
       </c>
       <c r="N696">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="697" spans="1:14" x14ac:dyDescent="0.35">
@@ -30528,7 +30541,7 @@
         <v>2911191.7370000002</v>
       </c>
       <c r="N697">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="698" spans="1:14" x14ac:dyDescent="0.35">
@@ -30564,7 +30577,7 @@
         <v>1742540.9650000001</v>
       </c>
       <c r="N698">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="699" spans="1:14" x14ac:dyDescent="0.35">
@@ -30600,7 +30613,7 @@
         <v>574904.47560000001</v>
       </c>
       <c r="N699">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="700" spans="1:14" x14ac:dyDescent="0.35">
@@ -30636,7 +30649,7 @@
         <v>817175.11970000004</v>
       </c>
       <c r="N700">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="701" spans="1:14" x14ac:dyDescent="0.35">
@@ -30672,7 +30685,7 @@
         <v>926077.06539999996</v>
       </c>
       <c r="N701">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="702" spans="1:14" x14ac:dyDescent="0.35">
@@ -30708,7 +30721,7 @@
         <v>486205.99310000002</v>
       </c>
       <c r="N702">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="703" spans="1:14" x14ac:dyDescent="0.35">
@@ -30744,7 +30757,7 @@
         <v>1404790.5430000001</v>
       </c>
       <c r="N703">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="704" spans="1:14" x14ac:dyDescent="0.35">
@@ -30780,7 +30793,7 @@
         <v>1005243.63</v>
       </c>
       <c r="N704">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="705" spans="1:14" x14ac:dyDescent="0.35">
@@ -30816,7 +30829,7 @@
         <v>3202553.6570000001</v>
       </c>
       <c r="N705">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="706" spans="1:14" x14ac:dyDescent="0.35">
@@ -30852,7 +30865,7 @@
         <v>972173.10569999996</v>
       </c>
       <c r="N706">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="707" spans="1:14" x14ac:dyDescent="0.35">
@@ -30888,7 +30901,7 @@
         <v>1455833.173</v>
       </c>
       <c r="N707">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="708" spans="1:14" x14ac:dyDescent="0.35">
@@ -30924,7 +30937,7 @@
         <v>477032.66070000001</v>
       </c>
       <c r="N708">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="709" spans="1:14" x14ac:dyDescent="0.35">
@@ -30960,7 +30973,7 @@
         <v>365798.14630000002</v>
       </c>
       <c r="N709">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="710" spans="1:14" x14ac:dyDescent="0.35">
@@ -30996,7 +31009,7 @@
         <v>11141928.6</v>
       </c>
       <c r="N710">
-        <v>0.15</v>
+        <v>1.5E-3</v>
       </c>
     </row>
     <row r="711" spans="1:14" x14ac:dyDescent="0.35">
@@ -31032,7 +31045,7 @@
         <v>1503875.828</v>
       </c>
       <c r="N711">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="712" spans="1:14" x14ac:dyDescent="0.35">
@@ -31068,7 +31081,7 @@
         <v>5096240.3310000002</v>
       </c>
       <c r="N712">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="713" spans="1:14" x14ac:dyDescent="0.35">
@@ -31104,7 +31117,7 @@
         <v>375478.76919999998</v>
       </c>
       <c r="N713">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="714" spans="1:14" x14ac:dyDescent="0.35">
@@ -31140,7 +31153,7 @@
         <v>1249536.6910000001</v>
       </c>
       <c r="N714">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="715" spans="1:14" x14ac:dyDescent="0.35">
@@ -31176,7 +31189,7 @@
         <v>3769102.5989999999</v>
       </c>
       <c r="N715">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="716" spans="1:14" x14ac:dyDescent="0.35">
@@ -31212,7 +31225,7 @@
         <v>5765490.3399999999</v>
       </c>
       <c r="N716">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="717" spans="1:14" x14ac:dyDescent="0.35">
@@ -31248,7 +31261,7 @@
         <v>2773182.97</v>
       </c>
       <c r="N717">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="718" spans="1:14" x14ac:dyDescent="0.35">
@@ -31284,7 +31297,7 @@
         <v>1795066.64</v>
       </c>
       <c r="N718">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="719" spans="1:14" x14ac:dyDescent="0.35">
@@ -31320,7 +31333,7 @@
         <v>457705.25809999998</v>
       </c>
       <c r="N719">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="720" spans="1:14" x14ac:dyDescent="0.35">
@@ -31392,7 +31405,7 @@
         <v>10796568.57</v>
       </c>
       <c r="N721">
-        <v>0.15</v>
+        <v>1.5E-3</v>
       </c>
     </row>
     <row r="722" spans="1:14" x14ac:dyDescent="0.35">
@@ -31428,7 +31441,7 @@
         <v>1387943.2379999999</v>
       </c>
       <c r="N722">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="723" spans="1:14" x14ac:dyDescent="0.35">
@@ -31464,7 +31477,7 @@
         <v>6566315.2560000001</v>
       </c>
       <c r="N723">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="724" spans="1:14" x14ac:dyDescent="0.35">
@@ -31500,7 +31513,7 @@
         <v>2573602.6519999998</v>
       </c>
       <c r="N724">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="725" spans="1:14" x14ac:dyDescent="0.35">
@@ -31572,7 +31585,7 @@
         <v>1465977.7790000001</v>
       </c>
       <c r="N726">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="727" spans="1:14" x14ac:dyDescent="0.35">
@@ -31608,7 +31621,7 @@
         <v>1061207.8659999999</v>
       </c>
       <c r="N727">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="728" spans="1:14" x14ac:dyDescent="0.35">
@@ -31644,7 +31657,7 @@
         <v>2320323.969</v>
       </c>
       <c r="N728">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="729" spans="1:14" x14ac:dyDescent="0.35">
@@ -31680,7 +31693,7 @@
         <v>4600874.7439999999</v>
       </c>
       <c r="N729">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="730" spans="1:14" x14ac:dyDescent="0.35">
@@ -31716,7 +31729,7 @@
         <v>1626496.209</v>
       </c>
       <c r="N730">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="731" spans="1:14" x14ac:dyDescent="0.35">
@@ -31752,7 +31765,7 @@
         <v>695054.57030000002</v>
       </c>
       <c r="N731">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="732" spans="1:14" x14ac:dyDescent="0.35">
@@ -31788,7 +31801,7 @@
         <v>1803877.352</v>
       </c>
       <c r="N732">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="733" spans="1:14" x14ac:dyDescent="0.35">
@@ -31824,7 +31837,7 @@
         <v>1248535.514</v>
       </c>
       <c r="N733">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="734" spans="1:14" x14ac:dyDescent="0.35">
@@ -31860,7 +31873,7 @@
         <v>3479533.3029999998</v>
       </c>
       <c r="N734">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="735" spans="1:14" x14ac:dyDescent="0.35">
@@ -31896,7 +31909,7 @@
         <v>869234.73959999997</v>
       </c>
       <c r="N735">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="736" spans="1:14" x14ac:dyDescent="0.35">
@@ -31932,7 +31945,7 @@
         <v>2320514.372</v>
       </c>
       <c r="N736">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="737" spans="1:14" x14ac:dyDescent="0.35">
@@ -31968,7 +31981,7 @@
         <v>3457068.3319999999</v>
       </c>
       <c r="N737">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="738" spans="1:14" x14ac:dyDescent="0.35">
@@ -32004,7 +32017,7 @@
         <v>4430590.1500000004</v>
       </c>
       <c r="N738">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="739" spans="1:14" x14ac:dyDescent="0.35">
@@ -32040,7 +32053,7 @@
         <v>30267507.93</v>
       </c>
       <c r="N739">
-        <v>0.42</v>
+        <v>4.1999999999999997E-3</v>
       </c>
     </row>
     <row r="740" spans="1:14" x14ac:dyDescent="0.35">
@@ -32076,7 +32089,7 @@
         <v>897955.02540000004</v>
       </c>
       <c r="N740">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="741" spans="1:14" x14ac:dyDescent="0.35">
@@ -32112,7 +32125,7 @@
         <v>1681095.3230000001</v>
       </c>
       <c r="N741">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="742" spans="1:14" x14ac:dyDescent="0.35">
@@ -32148,7 +32161,7 @@
         <v>1092767.872</v>
       </c>
       <c r="N742">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="743" spans="1:14" x14ac:dyDescent="0.35">
@@ -32184,7 +32197,7 @@
         <v>25886903.829999998</v>
       </c>
       <c r="N743">
-        <v>0.36</v>
+        <v>3.5999999999999999E-3</v>
       </c>
     </row>
     <row r="744" spans="1:14" x14ac:dyDescent="0.35">
@@ -32220,7 +32233,7 @@
         <v>795503.89599999995</v>
       </c>
       <c r="N744">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="745" spans="1:14" x14ac:dyDescent="0.35">
@@ -32256,7 +32269,7 @@
         <v>1334011.892</v>
       </c>
       <c r="N745">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="746" spans="1:14" x14ac:dyDescent="0.35">
@@ -32292,7 +32305,7 @@
         <v>2310378.0189999999</v>
       </c>
       <c r="N746">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="747" spans="1:14" x14ac:dyDescent="0.35">
@@ -32328,7 +32341,7 @@
         <v>16738870.73</v>
       </c>
       <c r="N747">
-        <v>0.22999999999999901</v>
+        <v>2.29999999999999E-3</v>
       </c>
     </row>
     <row r="748" spans="1:14" x14ac:dyDescent="0.35">
@@ -32400,7 +32413,7 @@
         <v>786579.30090000003</v>
       </c>
       <c r="N749">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="750" spans="1:14" x14ac:dyDescent="0.35">
@@ -32436,7 +32449,7 @@
         <v>3175398.8</v>
       </c>
       <c r="N750">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="751" spans="1:14" x14ac:dyDescent="0.35">
@@ -32472,7 +32485,7 @@
         <v>14690122.689999999</v>
       </c>
       <c r="N751">
-        <v>0.2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="752" spans="1:14" x14ac:dyDescent="0.35">
@@ -32508,7 +32521,7 @@
         <v>858632.89489999996</v>
       </c>
       <c r="N752">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="753" spans="1:14" x14ac:dyDescent="0.35">
@@ -32544,7 +32557,7 @@
         <v>10066150.449999999</v>
       </c>
       <c r="N753">
-        <v>0.13999999999999899</v>
+        <v>1.3999999999999898E-3</v>
       </c>
     </row>
     <row r="754" spans="1:14" x14ac:dyDescent="0.35">
@@ -32580,7 +32593,7 @@
         <v>3005786.594</v>
       </c>
       <c r="N754">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="755" spans="1:14" x14ac:dyDescent="0.35">
@@ -32652,7 +32665,7 @@
         <v>13416322.699999999</v>
       </c>
       <c r="N756">
-        <v>0.19</v>
+        <v>1.9E-3</v>
       </c>
     </row>
     <row r="757" spans="1:14" x14ac:dyDescent="0.35">
@@ -32760,7 +32773,7 @@
         <v>5358401.6220000004</v>
       </c>
       <c r="N759">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="760" spans="1:14" x14ac:dyDescent="0.35">
@@ -32796,7 +32809,7 @@
         <v>2794381.1719999998</v>
       </c>
       <c r="N760">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="761" spans="1:14" x14ac:dyDescent="0.35">
@@ -32832,7 +32845,7 @@
         <v>685610.29070000001</v>
       </c>
       <c r="N761">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="762" spans="1:14" x14ac:dyDescent="0.35">
@@ -32868,7 +32881,7 @@
         <v>6324993.0920000002</v>
       </c>
       <c r="N762">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="763" spans="1:14" x14ac:dyDescent="0.35">
@@ -32904,7 +32917,7 @@
         <v>5827671.9340000004</v>
       </c>
       <c r="N763">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="764" spans="1:14" x14ac:dyDescent="0.35">
@@ -32940,7 +32953,7 @@
         <v>833047.10640000005</v>
       </c>
       <c r="N764">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="765" spans="1:14" x14ac:dyDescent="0.35">
@@ -32976,7 +32989,7 @@
         <v>1327222.7009999999</v>
       </c>
       <c r="N765">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="766" spans="1:14" x14ac:dyDescent="0.35">
@@ -33012,7 +33025,7 @@
         <v>386214.62459999998</v>
       </c>
       <c r="N766">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="767" spans="1:14" x14ac:dyDescent="0.35">
@@ -33048,7 +33061,7 @@
         <v>2340152.8560000001</v>
       </c>
       <c r="N767">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="768" spans="1:14" x14ac:dyDescent="0.35">
@@ -33084,7 +33097,7 @@
         <v>1484799.2209999999</v>
       </c>
       <c r="N768">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="769" spans="1:14" x14ac:dyDescent="0.35">
@@ -33120,7 +33133,7 @@
         <v>488827.27439999999</v>
       </c>
       <c r="N769">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="770" spans="1:14" x14ac:dyDescent="0.35">
@@ -33156,7 +33169,7 @@
         <v>7823185.8210000005</v>
       </c>
       <c r="N770">
-        <v>0.11</v>
+        <v>1.1000000000000001E-3</v>
       </c>
     </row>
     <row r="771" spans="1:14" x14ac:dyDescent="0.35">
@@ -33192,7 +33205,7 @@
         <v>4180412.0109999999</v>
       </c>
       <c r="N771">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="772" spans="1:14" x14ac:dyDescent="0.35">
@@ -33228,7 +33241,7 @@
         <v>3144059.389</v>
       </c>
       <c r="N772">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="773" spans="1:14" x14ac:dyDescent="0.35">
@@ -33264,7 +33277,7 @@
         <v>2901256.855</v>
       </c>
       <c r="N773">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="774" spans="1:14" x14ac:dyDescent="0.35">
@@ -33300,7 +33313,7 @@
         <v>3155013.84</v>
       </c>
       <c r="N774">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="775" spans="1:14" x14ac:dyDescent="0.35">
@@ -33372,7 +33385,7 @@
         <v>1639992.0759999999</v>
       </c>
       <c r="N776">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="777" spans="1:14" x14ac:dyDescent="0.35">
@@ -33408,7 +33421,7 @@
         <v>7603663.6490000002</v>
       </c>
       <c r="N777">
-        <v>0.11</v>
+        <v>1.1000000000000001E-3</v>
       </c>
     </row>
     <row r="778" spans="1:14" x14ac:dyDescent="0.35">
@@ -33444,7 +33457,7 @@
         <v>1043340.849</v>
       </c>
       <c r="N778">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="779" spans="1:14" x14ac:dyDescent="0.35">
@@ -33516,7 +33529,7 @@
         <v>19863781.219999999</v>
       </c>
       <c r="N780">
-        <v>0.27999999999999903</v>
+        <v>2.7999999999999904E-3</v>
       </c>
     </row>
     <row r="781" spans="1:14" x14ac:dyDescent="0.35">
@@ -33552,7 +33565,7 @@
         <v>6945871.1330000004</v>
       </c>
       <c r="N781">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="782" spans="1:14" x14ac:dyDescent="0.35">
@@ -33588,7 +33601,7 @@
         <v>4497042.4400000004</v>
       </c>
       <c r="N782">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="783" spans="1:14" x14ac:dyDescent="0.35">
@@ -33624,7 +33637,7 @@
         <v>2728494.0150000001</v>
       </c>
       <c r="N783">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="784" spans="1:14" x14ac:dyDescent="0.35">
@@ -33660,7 +33673,7 @@
         <v>4961322.3380000005</v>
       </c>
       <c r="N784">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="785" spans="1:14" x14ac:dyDescent="0.35">
@@ -33696,7 +33709,7 @@
         <v>4750842.5420000004</v>
       </c>
       <c r="N785">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="786" spans="1:14" x14ac:dyDescent="0.35">
@@ -33732,7 +33745,7 @@
         <v>7969825.3559999997</v>
       </c>
       <c r="N786">
-        <v>0.11</v>
+        <v>1.1000000000000001E-3</v>
       </c>
     </row>
     <row r="787" spans="1:14" x14ac:dyDescent="0.35">
@@ -33768,7 +33781,7 @@
         <v>11246074.93</v>
       </c>
       <c r="N787">
-        <v>0.16</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="788" spans="1:14" x14ac:dyDescent="0.35">
@@ -33804,7 +33817,7 @@
         <v>1654137.6540000001</v>
       </c>
       <c r="N788">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="789" spans="1:14" x14ac:dyDescent="0.35">
@@ -33876,7 +33889,7 @@
         <v>1251273.3629999999</v>
       </c>
       <c r="N790">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="791" spans="1:14" x14ac:dyDescent="0.35">
@@ -33912,7 +33925,7 @@
         <v>771344.88919999998</v>
       </c>
       <c r="N791">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="792" spans="1:14" x14ac:dyDescent="0.35">
@@ -34020,7 +34033,7 @@
         <v>1481513.75</v>
       </c>
       <c r="N794">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="795" spans="1:14" x14ac:dyDescent="0.35">
@@ -34128,7 +34141,7 @@
         <v>1476834.473</v>
       </c>
       <c r="N797">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="798" spans="1:14" x14ac:dyDescent="0.35">
@@ -34164,7 +34177,7 @@
         <v>365278.2953</v>
       </c>
       <c r="N798">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="799" spans="1:14" x14ac:dyDescent="0.35">
@@ -34200,7 +34213,7 @@
         <v>1310312.1939999999</v>
       </c>
       <c r="N799">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="800" spans="1:14" x14ac:dyDescent="0.35">
@@ -34236,7 +34249,7 @@
         <v>567778.91879999998</v>
       </c>
       <c r="N800">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="801" spans="1:14" x14ac:dyDescent="0.35">
@@ -34272,7 +34285,7 @@
         <v>4908791.0559999999</v>
       </c>
       <c r="N801">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="802" spans="1:14" x14ac:dyDescent="0.35">
@@ -34308,7 +34321,7 @@
         <v>1546712.0419999999</v>
       </c>
       <c r="N802">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="803" spans="1:14" x14ac:dyDescent="0.35">
@@ -34344,7 +34357,7 @@
         <v>2281995.034</v>
       </c>
       <c r="N803">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="804" spans="1:14" x14ac:dyDescent="0.35">
@@ -34416,7 +34429,7 @@
         <v>845814.41619999998</v>
       </c>
       <c r="N805">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="806" spans="1:14" x14ac:dyDescent="0.35">
@@ -34452,7 +34465,7 @@
         <v>5115855.4919999996</v>
       </c>
       <c r="N806">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="807" spans="1:14" x14ac:dyDescent="0.35">
@@ -34488,7 +34501,7 @@
         <v>687456.64099999995</v>
       </c>
       <c r="N807">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="808" spans="1:14" x14ac:dyDescent="0.35">
@@ -34524,7 +34537,7 @@
         <v>3373065.977</v>
       </c>
       <c r="N808">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="809" spans="1:14" x14ac:dyDescent="0.35">
@@ -34560,7 +34573,7 @@
         <v>1564029.4569999999</v>
       </c>
       <c r="N809">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="810" spans="1:14" x14ac:dyDescent="0.35">
@@ -34596,7 +34609,7 @@
         <v>888733.16740000003</v>
       </c>
       <c r="N810">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="811" spans="1:14" x14ac:dyDescent="0.35">
@@ -34632,7 +34645,7 @@
         <v>492606.02110000001</v>
       </c>
       <c r="N811">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="812" spans="1:14" x14ac:dyDescent="0.35">
@@ -34668,7 +34681,7 @@
         <v>615170.48820000002</v>
       </c>
       <c r="N812">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="813" spans="1:14" x14ac:dyDescent="0.35">
@@ -34704,7 +34717,7 @@
         <v>4790280.1789999995</v>
       </c>
       <c r="N813">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="814" spans="1:14" x14ac:dyDescent="0.35">
@@ -34740,7 +34753,7 @@
         <v>5359087.7520000003</v>
       </c>
       <c r="N814">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="815" spans="1:14" x14ac:dyDescent="0.35">
@@ -34776,7 +34789,7 @@
         <v>2925980.9040000001</v>
       </c>
       <c r="N815">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="816" spans="1:14" x14ac:dyDescent="0.35">
@@ -34812,7 +34825,7 @@
         <v>3209674.5869999998</v>
       </c>
       <c r="N816">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="817" spans="1:14" x14ac:dyDescent="0.35">
@@ -34848,7 +34861,7 @@
         <v>5106905.6119999997</v>
       </c>
       <c r="N817">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="818" spans="1:14" x14ac:dyDescent="0.35">
@@ -34884,7 +34897,7 @@
         <v>1553451.3689999999</v>
       </c>
       <c r="N818">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="819" spans="1:14" x14ac:dyDescent="0.35">
@@ -34920,7 +34933,7 @@
         <v>694281.87410000002</v>
       </c>
       <c r="N819">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="820" spans="1:14" x14ac:dyDescent="0.35">
@@ -34956,7 +34969,7 @@
         <v>1153656.274</v>
       </c>
       <c r="N820">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="821" spans="1:14" x14ac:dyDescent="0.35">
@@ -34992,7 +35005,7 @@
         <v>10118635.130000001</v>
       </c>
       <c r="N821">
-        <v>0.13999999999999899</v>
+        <v>1.3999999999999898E-3</v>
       </c>
     </row>
     <row r="822" spans="1:14" x14ac:dyDescent="0.35">
@@ -35028,7 +35041,7 @@
         <v>545774.71770000004</v>
       </c>
       <c r="N822">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="823" spans="1:14" x14ac:dyDescent="0.35">
@@ -35100,7 +35113,7 @@
         <v>454842.17509999999</v>
       </c>
       <c r="N824">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="825" spans="1:14" x14ac:dyDescent="0.35">
@@ -35136,7 +35149,7 @@
         <v>3276763.7740000002</v>
       </c>
       <c r="N825">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="826" spans="1:14" x14ac:dyDescent="0.35">
@@ -35172,7 +35185,7 @@
         <v>806050.83219999995</v>
       </c>
       <c r="N826">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="827" spans="1:14" x14ac:dyDescent="0.35">
@@ -35208,7 +35221,7 @@
         <v>2445020.108</v>
       </c>
       <c r="N827">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="828" spans="1:14" x14ac:dyDescent="0.35">
@@ -35244,7 +35257,7 @@
         <v>3037197.0759999999</v>
       </c>
       <c r="N828">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="829" spans="1:14" x14ac:dyDescent="0.35">
@@ -35280,7 +35293,7 @@
         <v>7724501.1969999997</v>
       </c>
       <c r="N829">
-        <v>0.11</v>
+        <v>1.1000000000000001E-3</v>
       </c>
     </row>
     <row r="830" spans="1:14" x14ac:dyDescent="0.35">
@@ -35316,7 +35329,7 @@
         <v>2189571.3569999998</v>
       </c>
       <c r="N830">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="831" spans="1:14" x14ac:dyDescent="0.35">
@@ -35352,7 +35365,7 @@
         <v>42235529.600000001</v>
       </c>
       <c r="N831">
-        <v>0.57999999999999996</v>
+        <v>5.7999999999999996E-3</v>
       </c>
     </row>
     <row r="832" spans="1:14" x14ac:dyDescent="0.35">
@@ -35388,7 +35401,7 @@
         <v>17175914.949999999</v>
       </c>
       <c r="N832">
-        <v>0.24</v>
+        <v>2.3999999999999998E-3</v>
       </c>
     </row>
     <row r="833" spans="1:14" x14ac:dyDescent="0.35">
@@ -35424,7 +35437,7 @@
         <v>3478704.267</v>
       </c>
       <c r="N833">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="834" spans="1:14" x14ac:dyDescent="0.35">
@@ -35460,7 +35473,7 @@
         <v>1154835.378</v>
       </c>
       <c r="N834">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="835" spans="1:14" x14ac:dyDescent="0.35">
@@ -35496,7 +35509,7 @@
         <v>1833571.3319999999</v>
       </c>
       <c r="N835">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="836" spans="1:14" x14ac:dyDescent="0.35">
@@ -35532,7 +35545,7 @@
         <v>884173.34250000003</v>
       </c>
       <c r="N836">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="837" spans="1:14" x14ac:dyDescent="0.35">
@@ -35568,7 +35581,7 @@
         <v>3572998.5529999998</v>
       </c>
       <c r="N837">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="838" spans="1:14" x14ac:dyDescent="0.35">
@@ -35640,7 +35653,7 @@
         <v>561636.81189999997</v>
       </c>
       <c r="N839">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="840" spans="1:14" x14ac:dyDescent="0.35">
@@ -35676,7 +35689,7 @@
         <v>722043.19550000003</v>
       </c>
       <c r="N840">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="841" spans="1:14" x14ac:dyDescent="0.35">
@@ -35712,7 +35725,7 @@
         <v>441400.66110000003</v>
       </c>
       <c r="N841">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="842" spans="1:14" x14ac:dyDescent="0.35">
@@ -35748,7 +35761,7 @@
         <v>2492554.0249999999</v>
       </c>
       <c r="N842">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="843" spans="1:14" x14ac:dyDescent="0.35">
@@ -35784,7 +35797,7 @@
         <v>17892879.030000001</v>
       </c>
       <c r="N843">
-        <v>0.25</v>
+        <v>2.5000000000000001E-3</v>
       </c>
     </row>
     <row r="844" spans="1:14" x14ac:dyDescent="0.35">
@@ -35820,7 +35833,7 @@
         <v>764488.20429999998</v>
       </c>
       <c r="N844">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="845" spans="1:14" x14ac:dyDescent="0.35">
@@ -35856,7 +35869,7 @@
         <v>16051958.24</v>
       </c>
       <c r="N845">
-        <v>0.22</v>
+        <v>2.2000000000000001E-3</v>
       </c>
     </row>
     <row r="846" spans="1:14" x14ac:dyDescent="0.35">
@@ -35892,7 +35905,7 @@
         <v>1027956.1040000001</v>
       </c>
       <c r="N846">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="847" spans="1:14" x14ac:dyDescent="0.35">
@@ -35928,7 +35941,7 @@
         <v>495405.01199999999</v>
       </c>
       <c r="N847">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="848" spans="1:14" x14ac:dyDescent="0.35">
@@ -35964,7 +35977,7 @@
         <v>581839.61569999997</v>
       </c>
       <c r="N848">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="849" spans="1:14" x14ac:dyDescent="0.35">
@@ -36000,7 +36013,7 @@
         <v>3734128.1680000001</v>
       </c>
       <c r="N849">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="850" spans="1:14" x14ac:dyDescent="0.35">
@@ -36036,7 +36049,7 @@
         <v>27134810.66</v>
       </c>
       <c r="N850">
-        <v>0.38</v>
+        <v>3.8E-3</v>
       </c>
     </row>
     <row r="851" spans="1:14" x14ac:dyDescent="0.35">
@@ -36108,7 +36121,7 @@
         <v>1241365.233</v>
       </c>
       <c r="N852">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="853" spans="1:14" x14ac:dyDescent="0.35">
@@ -36180,7 +36193,7 @@
         <v>1532473.8529999999</v>
       </c>
       <c r="N854">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="855" spans="1:14" x14ac:dyDescent="0.35">
@@ -36216,7 +36229,7 @@
         <v>2526791.986</v>
       </c>
       <c r="N855">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="856" spans="1:14" x14ac:dyDescent="0.35">
@@ -36288,7 +36301,7 @@
         <v>16165115.76</v>
       </c>
       <c r="N857">
-        <v>0.22</v>
+        <v>2.2000000000000001E-3</v>
       </c>
     </row>
     <row r="858" spans="1:14" x14ac:dyDescent="0.35">
@@ -36324,7 +36337,7 @@
         <v>1576414.3529999999</v>
       </c>
       <c r="N858">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="859" spans="1:14" x14ac:dyDescent="0.35">
@@ -36360,7 +36373,7 @@
         <v>4608584.38</v>
       </c>
       <c r="N859">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="860" spans="1:14" x14ac:dyDescent="0.35">
@@ -36432,7 +36445,7 @@
         <v>4552138.6789999995</v>
       </c>
       <c r="N861">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="862" spans="1:14" x14ac:dyDescent="0.35">
@@ -36468,7 +36481,7 @@
         <v>5549147.3190000001</v>
       </c>
       <c r="N862">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="863" spans="1:14" x14ac:dyDescent="0.35">
@@ -36504,7 +36517,7 @@
         <v>5478746.9309999999</v>
       </c>
       <c r="N863">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="864" spans="1:14" x14ac:dyDescent="0.35">
@@ -36540,7 +36553,7 @@
         <v>1521979.3659999999</v>
       </c>
       <c r="N864">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="865" spans="1:14" x14ac:dyDescent="0.35">
@@ -36576,7 +36589,7 @@
         <v>2293887.8629999999</v>
       </c>
       <c r="N865">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="866" spans="1:14" x14ac:dyDescent="0.35">
@@ -36612,7 +36625,7 @@
         <v>2428285.1430000002</v>
       </c>
       <c r="N866">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="867" spans="1:14" x14ac:dyDescent="0.35">
@@ -36648,7 +36661,7 @@
         <v>4927393.6890000002</v>
       </c>
       <c r="N867">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="868" spans="1:14" x14ac:dyDescent="0.35">
@@ -36684,7 +36697,7 @@
         <v>4690627.5930000003</v>
       </c>
       <c r="N868">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="869" spans="1:14" x14ac:dyDescent="0.35">
@@ -36720,7 +36733,7 @@
         <v>9789355.7520000003</v>
       </c>
       <c r="N869">
-        <v>0.13999999999999899</v>
+        <v>1.3999999999999898E-3</v>
       </c>
     </row>
     <row r="870" spans="1:14" x14ac:dyDescent="0.35">
@@ -36756,7 +36769,7 @@
         <v>3066829.108</v>
       </c>
       <c r="N870">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="871" spans="1:14" x14ac:dyDescent="0.35">
@@ -36792,7 +36805,7 @@
         <v>2250860.9109999998</v>
       </c>
       <c r="N871">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="872" spans="1:14" x14ac:dyDescent="0.35">
@@ -36900,7 +36913,7 @@
         <v>2183911.0189999999</v>
       </c>
       <c r="N874">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="875" spans="1:14" x14ac:dyDescent="0.35">
@@ -36972,7 +36985,7 @@
         <v>5418363.1390000004</v>
       </c>
       <c r="N876">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="877" spans="1:14" x14ac:dyDescent="0.35">
@@ -37008,7 +37021,7 @@
         <v>2662274.588</v>
       </c>
       <c r="N877">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="878" spans="1:14" x14ac:dyDescent="0.35">
@@ -37044,7 +37057,7 @@
         <v>468997.54670000001</v>
       </c>
       <c r="N878">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="879" spans="1:14" x14ac:dyDescent="0.35">
@@ -37080,7 +37093,7 @@
         <v>3805931.5729999999</v>
       </c>
       <c r="N879">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="880" spans="1:14" x14ac:dyDescent="0.35">
@@ -37116,7 +37129,7 @@
         <v>12576959.779999999</v>
       </c>
       <c r="N880">
-        <v>0.16999999999999901</v>
+        <v>1.6999999999999901E-3</v>
       </c>
     </row>
     <row r="881" spans="1:14" x14ac:dyDescent="0.35">
@@ -37152,7 +37165,7 @@
         <v>1332109.0190000001</v>
       </c>
       <c r="N881">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="882" spans="1:14" x14ac:dyDescent="0.35">
@@ -37188,7 +37201,7 @@
         <v>5033130.0760000004</v>
       </c>
       <c r="N882">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="883" spans="1:14" x14ac:dyDescent="0.35">
@@ -37224,7 +37237,7 @@
         <v>4913967.6380000003</v>
       </c>
       <c r="N883">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="884" spans="1:14" x14ac:dyDescent="0.35">
@@ -37260,7 +37273,7 @@
         <v>3583495.1039999998</v>
       </c>
       <c r="N884">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="885" spans="1:14" x14ac:dyDescent="0.35">
@@ -37296,7 +37309,7 @@
         <v>1581973.1259999999</v>
       </c>
       <c r="N885">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="886" spans="1:14" x14ac:dyDescent="0.35">
@@ -37332,7 +37345,7 @@
         <v>1299260.58</v>
       </c>
       <c r="N886">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="887" spans="1:14" x14ac:dyDescent="0.35">
@@ -37368,7 +37381,7 @@
         <v>18222222.359999999</v>
       </c>
       <c r="N887">
-        <v>0.25</v>
+        <v>2.5000000000000001E-3</v>
       </c>
     </row>
     <row r="888" spans="1:14" x14ac:dyDescent="0.35">
@@ -37404,7 +37417,7 @@
         <v>1187572.0430000001</v>
       </c>
       <c r="N888">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="889" spans="1:14" x14ac:dyDescent="0.35">
@@ -37476,7 +37489,7 @@
         <v>762655.87060000002</v>
       </c>
       <c r="N890">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="891" spans="1:14" x14ac:dyDescent="0.35">
@@ -37512,7 +37525,7 @@
         <v>1656385.2490000001</v>
       </c>
       <c r="N891">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="892" spans="1:14" x14ac:dyDescent="0.35">
@@ -37548,7 +37561,7 @@
         <v>3217948.8119999999</v>
       </c>
       <c r="N892">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="893" spans="1:14" x14ac:dyDescent="0.35">
@@ -37584,7 +37597,7 @@
         <v>3857844.4909999999</v>
       </c>
       <c r="N893">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="894" spans="1:14" x14ac:dyDescent="0.35">
@@ -37620,7 +37633,7 @@
         <v>6339701.5659999996</v>
       </c>
       <c r="N894">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="895" spans="1:14" x14ac:dyDescent="0.35">
@@ -37656,7 +37669,7 @@
         <v>1186351.554</v>
       </c>
       <c r="N895">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="896" spans="1:14" x14ac:dyDescent="0.35">
@@ -37692,7 +37705,7 @@
         <v>2907967.8960000002</v>
       </c>
       <c r="N896">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="897" spans="1:14" x14ac:dyDescent="0.35">
@@ -37728,7 +37741,7 @@
         <v>1020492.327</v>
       </c>
       <c r="N897">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="898" spans="1:14" x14ac:dyDescent="0.35">
@@ -37764,7 +37777,7 @@
         <v>11447537.279999999</v>
       </c>
       <c r="N898">
-        <v>0.16</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="899" spans="1:14" x14ac:dyDescent="0.35">
@@ -37800,7 +37813,7 @@
         <v>2153617.673</v>
       </c>
       <c r="N899">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="900" spans="1:14" x14ac:dyDescent="0.35">
@@ -37836,7 +37849,7 @@
         <v>1241480.2620000001</v>
       </c>
       <c r="N900">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="901" spans="1:14" x14ac:dyDescent="0.35">
@@ -37872,7 +37885,7 @@
         <v>1966607.6040000001</v>
       </c>
       <c r="N901">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="902" spans="1:14" x14ac:dyDescent="0.35">
@@ -37908,7 +37921,7 @@
         <v>499114.33689999999</v>
       </c>
       <c r="N902">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="903" spans="1:14" x14ac:dyDescent="0.35">
@@ -37944,7 +37957,7 @@
         <v>11822123.18</v>
       </c>
       <c r="N903">
-        <v>0.16</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="904" spans="1:14" x14ac:dyDescent="0.35">
@@ -37980,7 +37993,7 @@
         <v>375271.04590000003</v>
       </c>
       <c r="N904">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="905" spans="1:14" x14ac:dyDescent="0.35">
@@ -38088,7 +38101,7 @@
         <v>1450693.6529999999</v>
       </c>
       <c r="N907">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="908" spans="1:14" x14ac:dyDescent="0.35">
@@ -38124,7 +38137,7 @@
         <v>2878170.99</v>
       </c>
       <c r="N908">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="909" spans="1:14" x14ac:dyDescent="0.35">
@@ -38160,7 +38173,7 @@
         <v>45380581.5</v>
       </c>
       <c r="N909">
-        <v>0.63</v>
+        <v>6.3E-3</v>
       </c>
     </row>
     <row r="910" spans="1:14" x14ac:dyDescent="0.35">
@@ -38196,7 +38209,7 @@
         <v>1809437.469</v>
       </c>
       <c r="N910">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="911" spans="1:14" x14ac:dyDescent="0.35">
@@ -38232,7 +38245,7 @@
         <v>1106219.0020000001</v>
       </c>
       <c r="N911">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="912" spans="1:14" x14ac:dyDescent="0.35">
@@ -38268,7 +38281,7 @@
         <v>3487321.9879999999</v>
       </c>
       <c r="N912">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="913" spans="1:14" x14ac:dyDescent="0.35">
@@ -38304,7 +38317,7 @@
         <v>40481841.259999998</v>
       </c>
       <c r="N913">
-        <v>0.55999999999999905</v>
+        <v>5.5999999999999904E-3</v>
       </c>
     </row>
     <row r="914" spans="1:14" x14ac:dyDescent="0.35">
@@ -38340,7 +38353,7 @@
         <v>1556949.365</v>
       </c>
       <c r="N914">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="915" spans="1:14" x14ac:dyDescent="0.35">
@@ -38376,7 +38389,7 @@
         <v>3318533.1570000001</v>
       </c>
       <c r="N915">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="916" spans="1:14" x14ac:dyDescent="0.35">
@@ -38412,7 +38425,7 @@
         <v>2050814.1</v>
       </c>
       <c r="N916">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="917" spans="1:14" x14ac:dyDescent="0.35">
@@ -38448,7 +38461,7 @@
         <v>1635491.298</v>
       </c>
       <c r="N917">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="918" spans="1:14" x14ac:dyDescent="0.35">
@@ -38484,7 +38497,7 @@
         <v>1402988.5930000001</v>
       </c>
       <c r="N918">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="919" spans="1:14" x14ac:dyDescent="0.35">
@@ -38520,7 +38533,7 @@
         <v>11702100.41</v>
       </c>
       <c r="N919">
-        <v>0.16</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="920" spans="1:14" x14ac:dyDescent="0.35">
@@ -38592,7 +38605,7 @@
         <v>2541315.895</v>
       </c>
       <c r="N921">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="922" spans="1:14" x14ac:dyDescent="0.35">
@@ -38628,7 +38641,7 @@
         <v>16024469.029999999</v>
       </c>
       <c r="N922">
-        <v>0.22</v>
+        <v>2.2000000000000001E-3</v>
       </c>
     </row>
     <row r="923" spans="1:14" x14ac:dyDescent="0.35">
@@ -38664,7 +38677,7 @@
         <v>25348883.73</v>
       </c>
       <c r="N923">
-        <v>0.35</v>
+        <v>3.4999999999999996E-3</v>
       </c>
     </row>
     <row r="924" spans="1:14" x14ac:dyDescent="0.35">
@@ -38736,7 +38749,7 @@
         <v>3317845.358</v>
       </c>
       <c r="N925">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="926" spans="1:14" x14ac:dyDescent="0.35">
@@ -38772,7 +38785,7 @@
         <v>3759260.96</v>
       </c>
       <c r="N926">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="927" spans="1:14" x14ac:dyDescent="0.35">
@@ -38808,7 +38821,7 @@
         <v>3452099.66</v>
       </c>
       <c r="N927">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="928" spans="1:14" x14ac:dyDescent="0.35">
@@ -38844,7 +38857,7 @@
         <v>602383.84129999997</v>
       </c>
       <c r="N928">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="929" spans="1:14" x14ac:dyDescent="0.35">
@@ -38880,7 +38893,7 @@
         <v>15418398.210000001</v>
       </c>
       <c r="N929">
-        <v>0.21</v>
+        <v>2.0999999999999999E-3</v>
       </c>
     </row>
     <row r="930" spans="1:14" x14ac:dyDescent="0.35">
@@ -38916,7 +38929,7 @@
         <v>2950734.72</v>
       </c>
       <c r="N930">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="931" spans="1:14" x14ac:dyDescent="0.35">
@@ -38952,7 +38965,7 @@
         <v>768156.42099999997</v>
       </c>
       <c r="N931">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="932" spans="1:14" x14ac:dyDescent="0.35">
@@ -38988,7 +39001,7 @@
         <v>1013760.309</v>
       </c>
       <c r="N932">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="933" spans="1:14" x14ac:dyDescent="0.35">
@@ -39024,7 +39037,7 @@
         <v>1468406.182</v>
       </c>
       <c r="N933">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="934" spans="1:14" x14ac:dyDescent="0.35">
@@ -39060,7 +39073,7 @@
         <v>1286787.3289999999</v>
       </c>
       <c r="N934">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="935" spans="1:14" x14ac:dyDescent="0.35">
@@ -39096,7 +39109,7 @@
         <v>2958584.0430000001</v>
       </c>
       <c r="N935">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="936" spans="1:14" x14ac:dyDescent="0.35">
@@ -39132,7 +39145,7 @@
         <v>689404.68409999995</v>
       </c>
       <c r="N936">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="937" spans="1:14" x14ac:dyDescent="0.35">
@@ -39168,7 +39181,7 @@
         <v>776511.15190000006</v>
       </c>
       <c r="N937">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="938" spans="1:14" x14ac:dyDescent="0.35">
@@ -39204,7 +39217,7 @@
         <v>3344320.7009999999</v>
       </c>
       <c r="N938">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="939" spans="1:14" x14ac:dyDescent="0.35">
@@ -39240,7 +39253,7 @@
         <v>4901511.9009999996</v>
       </c>
       <c r="N939">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="940" spans="1:14" x14ac:dyDescent="0.35">
@@ -39306,7 +39319,7 @@
         <v>3748001429.9275098</v>
       </c>
       <c r="N941">
-        <v>51.83</v>
+        <v>0.51829999999999998</v>
       </c>
     </row>
     <row r="942" spans="1:14" x14ac:dyDescent="0.35">
@@ -39335,6 +39348,9 @@
       <c r="K942">
         <v>2.9000000000000001E-2</v>
       </c>
+      <c r="N942">
+        <v>0</v>
+      </c>
     </row>
     <row r="943" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A943" s="1">
@@ -39362,6 +39378,9 @@
       <c r="K943">
         <v>3.5999999999999997E-2</v>
       </c>
+      <c r="N943">
+        <v>0</v>
+      </c>
     </row>
     <row r="944" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A944" s="1">
@@ -39390,7 +39409,7 @@
         <v>37375481.799999997</v>
       </c>
       <c r="N944">
-        <v>0.52</v>
+        <v>5.1999999999999998E-3</v>
       </c>
     </row>
     <row r="945" spans="1:14" x14ac:dyDescent="0.35">
@@ -39420,7 +39439,7 @@
         <v>9030777.5470000003</v>
       </c>
       <c r="N945">
-        <v>0.13</v>
+        <v>1.2999999999999999E-3</v>
       </c>
     </row>
     <row r="946" spans="1:14" x14ac:dyDescent="0.35">
@@ -39510,7 +39529,7 @@
         <v>4595797.68</v>
       </c>
       <c r="N948">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="949" spans="1:14" x14ac:dyDescent="0.35">
@@ -39570,7 +39589,7 @@
         <v>2410855.6669999999</v>
       </c>
       <c r="N950">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="951" spans="1:14" x14ac:dyDescent="0.35">
@@ -39630,7 +39649,7 @@
         <v>1429676.9140000001</v>
       </c>
       <c r="N952">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="953" spans="1:14" x14ac:dyDescent="0.35">
@@ -39660,7 +39679,7 @@
         <v>1552275.0090000001</v>
       </c>
       <c r="N953">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="954" spans="1:14" x14ac:dyDescent="0.35">
@@ -39690,7 +39709,7 @@
         <v>6686963.5060000001</v>
       </c>
       <c r="N954">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="955" spans="1:14" x14ac:dyDescent="0.35">
@@ -39720,7 +39739,7 @@
         <v>25082655.280000001</v>
       </c>
       <c r="N955">
-        <v>0.35</v>
+        <v>3.4999999999999996E-3</v>
       </c>
     </row>
     <row r="956" spans="1:14" x14ac:dyDescent="0.35">
@@ -39750,7 +39769,7 @@
         <v>51461316.2346</v>
       </c>
       <c r="N956">
-        <v>0.7</v>
+        <v>6.9999999999999993E-3</v>
       </c>
     </row>
     <row r="957" spans="1:14" x14ac:dyDescent="0.35">
@@ -39786,7 +39805,7 @@
         <v>839381.70849999995</v>
       </c>
       <c r="N957">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="958" spans="1:14" x14ac:dyDescent="0.35">
@@ -39822,7 +39841,7 @@
         <v>725136.81929999997</v>
       </c>
       <c r="N958">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="959" spans="1:14" x14ac:dyDescent="0.35">
@@ -39858,7 +39877,7 @@
         <v>488176.27799999999</v>
       </c>
       <c r="N959">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="960" spans="1:14" x14ac:dyDescent="0.35">
@@ -39894,7 +39913,7 @@
         <v>1892695.297</v>
       </c>
       <c r="N960">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="961" spans="1:14" x14ac:dyDescent="0.35">
@@ -39966,7 +39985,7 @@
         <v>2676415.6</v>
       </c>
       <c r="N962">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="963" spans="1:14" x14ac:dyDescent="0.35">
@@ -40002,7 +40021,7 @@
         <v>861855.41899999999</v>
       </c>
       <c r="N963">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="964" spans="1:14" x14ac:dyDescent="0.35">
@@ -40038,7 +40057,7 @@
         <v>2668570.7390000001</v>
       </c>
       <c r="N964">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="965" spans="1:14" x14ac:dyDescent="0.35">
@@ -40074,7 +40093,7 @@
         <v>559433.12060000002</v>
       </c>
       <c r="N965">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="966" spans="1:14" x14ac:dyDescent="0.35">
@@ -40110,7 +40129,7 @@
         <v>1691922.6910000001</v>
       </c>
       <c r="N966">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="967" spans="1:14" x14ac:dyDescent="0.35">
@@ -40146,7 +40165,7 @@
         <v>763725.04070000001</v>
       </c>
       <c r="N967">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="968" spans="1:14" x14ac:dyDescent="0.35">
@@ -40182,7 +40201,7 @@
         <v>1624459.5330000001</v>
       </c>
       <c r="N968">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="969" spans="1:14" x14ac:dyDescent="0.35">
@@ -40218,7 +40237,7 @@
         <v>846783.70220000006</v>
       </c>
       <c r="N969">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="970" spans="1:14" x14ac:dyDescent="0.35">
@@ -40254,7 +40273,7 @@
         <v>12970203.09</v>
       </c>
       <c r="N970">
-        <v>0.18</v>
+        <v>1.8E-3</v>
       </c>
     </row>
     <row r="971" spans="1:14" x14ac:dyDescent="0.35">
@@ -40290,7 +40309,7 @@
         <v>2173325.568</v>
       </c>
       <c r="N971">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="972" spans="1:14" x14ac:dyDescent="0.35">
@@ -40362,7 +40381,7 @@
         <v>755131.77659999998</v>
       </c>
       <c r="N973">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="974" spans="1:14" x14ac:dyDescent="0.35">
@@ -40398,7 +40417,7 @@
         <v>1874410.997</v>
       </c>
       <c r="N974">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="975" spans="1:14" x14ac:dyDescent="0.35">
@@ -40434,7 +40453,7 @@
         <v>2803446.5320000001</v>
       </c>
       <c r="N975">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="976" spans="1:14" x14ac:dyDescent="0.35">
@@ -40470,7 +40489,7 @@
         <v>1469218.0589999999</v>
       </c>
       <c r="N976">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="977" spans="1:14" x14ac:dyDescent="0.35">
@@ -40506,7 +40525,7 @@
         <v>2340314.4870000002</v>
       </c>
       <c r="N977">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="978" spans="1:14" x14ac:dyDescent="0.35">
@@ -40542,7 +40561,7 @@
         <v>1793921.105</v>
       </c>
       <c r="N978">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="979" spans="1:14" x14ac:dyDescent="0.35">
@@ -40578,7 +40597,7 @@
         <v>2644980.2740000002</v>
       </c>
       <c r="N979">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="980" spans="1:14" x14ac:dyDescent="0.35">
@@ -40614,7 +40633,7 @@
         <v>1211264.754</v>
       </c>
       <c r="N980">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="981" spans="1:14" x14ac:dyDescent="0.35">
@@ -40650,7 +40669,7 @@
         <v>2612028.1030000001</v>
       </c>
       <c r="N981">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="982" spans="1:14" x14ac:dyDescent="0.35">
@@ -40686,7 +40705,7 @@
         <v>8207865.2379999999</v>
       </c>
       <c r="N982">
-        <v>0.11</v>
+        <v>1.1000000000000001E-3</v>
       </c>
     </row>
     <row r="983" spans="1:14" x14ac:dyDescent="0.35">
@@ -40722,7 +40741,7 @@
         <v>8465509.0089999996</v>
       </c>
       <c r="N983">
-        <v>0.12</v>
+        <v>1.1999999999999999E-3</v>
       </c>
     </row>
     <row r="984" spans="1:14" x14ac:dyDescent="0.35">
@@ -40758,7 +40777,7 @@
         <v>1895353.318</v>
       </c>
       <c r="N984">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="985" spans="1:14" x14ac:dyDescent="0.35">
@@ -40794,7 +40813,7 @@
         <v>4918046.4270000001</v>
       </c>
       <c r="N985">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="986" spans="1:14" x14ac:dyDescent="0.35">
@@ -40866,7 +40885,7 @@
         <v>2116242.33</v>
       </c>
       <c r="N987">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="988" spans="1:14" x14ac:dyDescent="0.35">
@@ -40902,7 +40921,7 @@
         <v>690790.87309999997</v>
       </c>
       <c r="N988">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="989" spans="1:14" x14ac:dyDescent="0.35">
@@ -40938,7 +40957,7 @@
         <v>5381050.5760000004</v>
       </c>
       <c r="N989">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="990" spans="1:14" x14ac:dyDescent="0.35">
@@ -40974,7 +40993,7 @@
         <v>754000.81819999998</v>
       </c>
       <c r="N990">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="991" spans="1:14" x14ac:dyDescent="0.35">
@@ -41046,7 +41065,7 @@
         <v>40555482.670000002</v>
       </c>
       <c r="N992">
-        <v>0.55999999999999905</v>
+        <v>5.5999999999999904E-3</v>
       </c>
     </row>
     <row r="993" spans="1:14" x14ac:dyDescent="0.35">
@@ -41082,7 +41101,7 @@
         <v>3613377.361</v>
       </c>
       <c r="N993">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="994" spans="1:14" x14ac:dyDescent="0.35">
@@ -41118,7 +41137,7 @@
         <v>3200626.159</v>
       </c>
       <c r="N994">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="995" spans="1:14" x14ac:dyDescent="0.35">
@@ -41154,7 +41173,7 @@
         <v>1786128.2760000001</v>
       </c>
       <c r="N995">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="996" spans="1:14" x14ac:dyDescent="0.35">
@@ -41190,7 +41209,7 @@
         <v>960933.74820000003</v>
       </c>
       <c r="N996">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="997" spans="1:14" x14ac:dyDescent="0.35">
@@ -41226,7 +41245,7 @@
         <v>1285667.8929999999</v>
       </c>
       <c r="N997">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="998" spans="1:14" x14ac:dyDescent="0.35">
@@ -41262,7 +41281,7 @@
         <v>1339516.216</v>
       </c>
       <c r="N998">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="999" spans="1:14" x14ac:dyDescent="0.35">
@@ -41298,7 +41317,7 @@
         <v>1961992.014</v>
       </c>
       <c r="N999">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="1000" spans="1:14" x14ac:dyDescent="0.35">
@@ -41334,7 +41353,7 @@
         <v>2387330.966</v>
       </c>
       <c r="N1000">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="1001" spans="1:14" x14ac:dyDescent="0.35">
@@ -41406,7 +41425,7 @@
         <v>2521853.2579999999</v>
       </c>
       <c r="N1002">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="1003" spans="1:14" x14ac:dyDescent="0.35">
@@ -41442,7 +41461,7 @@
         <v>5605193.5669999998</v>
       </c>
       <c r="N1003">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="1004" spans="1:14" x14ac:dyDescent="0.35">
@@ -41478,7 +41497,7 @@
         <v>4423946.9170000004</v>
       </c>
       <c r="N1004">
-        <v>0.06</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="1005" spans="1:14" x14ac:dyDescent="0.35">
@@ -41514,7 +41533,7 @@
         <v>751802.95440000005</v>
       </c>
       <c r="N1005">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="1006" spans="1:14" x14ac:dyDescent="0.35">
@@ -41550,7 +41569,7 @@
         <v>1832623.6040000001</v>
       </c>
       <c r="N1006">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="1007" spans="1:14" x14ac:dyDescent="0.35">
@@ -41586,7 +41605,7 @@
         <v>3385610.8939999999</v>
       </c>
       <c r="N1007">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="1008" spans="1:14" x14ac:dyDescent="0.35">
@@ -41622,7 +41641,7 @@
         <v>1944018.564</v>
       </c>
       <c r="N1008">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="1009" spans="1:14" x14ac:dyDescent="0.35">
@@ -41658,7 +41677,7 @@
         <v>3937176.5860000001</v>
       </c>
       <c r="N1009">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="1010" spans="1:14" x14ac:dyDescent="0.35">
@@ -41730,7 +41749,7 @@
         <v>6736005.0140000004</v>
       </c>
       <c r="N1011">
-        <v>0.09</v>
+        <v>8.9999999999999998E-4</v>
       </c>
     </row>
     <row r="1012" spans="1:14" x14ac:dyDescent="0.35">
@@ -41766,7 +41785,7 @@
         <v>706958.55359999998</v>
       </c>
       <c r="N1012">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="1013" spans="1:14" x14ac:dyDescent="0.35">
@@ -41838,7 +41857,7 @@
         <v>10590171.449999999</v>
       </c>
       <c r="N1014">
-        <v>0.15</v>
+        <v>1.5E-3</v>
       </c>
     </row>
     <row r="1015" spans="1:14" x14ac:dyDescent="0.35">
@@ -41874,7 +41893,7 @@
         <v>1072579.375</v>
       </c>
       <c r="N1015">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="1016" spans="1:14" x14ac:dyDescent="0.35">
@@ -41910,7 +41929,7 @@
         <v>1673318.3389999999</v>
       </c>
       <c r="N1016">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="1017" spans="1:14" x14ac:dyDescent="0.35">
@@ -41946,7 +41965,7 @@
         <v>7424054.1610000003</v>
       </c>
       <c r="N1017">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="1018" spans="1:14" x14ac:dyDescent="0.35">
@@ -41982,7 +42001,7 @@
         <v>597960.78940000001</v>
       </c>
       <c r="N1018">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="1019" spans="1:14" x14ac:dyDescent="0.35">
@@ -42018,7 +42037,7 @@
         <v>5346567.4579999996</v>
       </c>
       <c r="N1019">
-        <v>6.9999999999999896E-2</v>
+        <v>6.9999999999999891E-4</v>
       </c>
     </row>
     <row r="1020" spans="1:14" x14ac:dyDescent="0.35">
@@ -42054,7 +42073,7 @@
         <v>1356670.1839999999</v>
       </c>
       <c r="N1020">
-        <v>0.02</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="1021" spans="1:14" x14ac:dyDescent="0.35">
@@ -42090,7 +42109,7 @@
         <v>1001609.6</v>
       </c>
       <c r="N1021">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="1022" spans="1:14" x14ac:dyDescent="0.35">
@@ -42126,7 +42145,7 @@
         <v>2423193.8870000001</v>
       </c>
       <c r="N1022">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="1023" spans="1:14" x14ac:dyDescent="0.35">
@@ -42162,7 +42181,7 @@
         <v>1810657.156</v>
       </c>
       <c r="N1023">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="1024" spans="1:14" x14ac:dyDescent="0.35">
@@ -42198,7 +42217,7 @@
         <v>948450.29249999998</v>
       </c>
       <c r="N1024">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="1025" spans="1:14" x14ac:dyDescent="0.35">
@@ -42234,7 +42253,7 @@
         <v>5739435.8370000003</v>
       </c>
       <c r="N1025">
-        <v>0.08</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="1026" spans="1:14" x14ac:dyDescent="0.35">
@@ -42270,7 +42289,7 @@
         <v>2650332.9190000002</v>
       </c>
       <c r="N1026">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="1027" spans="1:14" x14ac:dyDescent="0.35">
@@ -42306,7 +42325,7 @@
         <v>799788.99320000003</v>
       </c>
       <c r="N1027">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="1028" spans="1:14" x14ac:dyDescent="0.35">
@@ -42342,7 +42361,7 @@
         <v>8452947.4100000001</v>
       </c>
       <c r="N1028">
-        <v>0.12</v>
+        <v>1.1999999999999999E-3</v>
       </c>
     </row>
     <row r="1029" spans="1:14" x14ac:dyDescent="0.35">
@@ -42378,7 +42397,7 @@
         <v>10164606.970000001</v>
       </c>
       <c r="N1029">
-        <v>0.13999999999999899</v>
+        <v>1.3999999999999898E-3</v>
       </c>
     </row>
     <row r="1030" spans="1:14" x14ac:dyDescent="0.35">
@@ -42408,7 +42427,7 @@
         <v>233248181.9989</v>
       </c>
       <c r="N1030">
-        <v>3.2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="1031" spans="1:14" x14ac:dyDescent="0.35">
@@ -42438,7 +42457,7 @@
         <v>288915926.19999999</v>
       </c>
       <c r="N1031">
-        <v>4</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="1032" spans="1:14" x14ac:dyDescent="0.35">
@@ -42468,7 +42487,7 @@
         <v>2000709.375</v>
       </c>
       <c r="N1032">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="1033" spans="1:14" x14ac:dyDescent="0.35">
@@ -42498,7 +42517,7 @@
         <v>290916635.57499999</v>
       </c>
       <c r="N1033">
-        <v>4.03</v>
+        <v>4.0300000000000002E-2</v>
       </c>
     </row>
     <row r="1034" spans="1:14" x14ac:dyDescent="0.35">
@@ -42534,7 +42553,7 @@
         <v>2760057.0249999999</v>
       </c>
       <c r="N1034">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="1035" spans="1:14" x14ac:dyDescent="0.35">
@@ -42570,7 +42589,7 @@
         <v>2817291.2710000002</v>
       </c>
       <c r="N1035">
-        <v>0.04</v>
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="1036" spans="1:14" x14ac:dyDescent="0.35">
@@ -42606,7 +42625,7 @@
         <v>2156089.2059999998</v>
       </c>
       <c r="N1036">
-        <v>0.03</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="1037" spans="1:14" x14ac:dyDescent="0.35">
@@ -42642,7 +42661,7 @@
         <v>28452608.440000001</v>
       </c>
       <c r="N1037">
-        <v>0.38999999999999901</v>
+        <v>3.8999999999999903E-3</v>
       </c>
     </row>
     <row r="1038" spans="1:14" x14ac:dyDescent="0.35">
@@ -42672,7 +42691,7 @@
         <v>36186045.942000002</v>
       </c>
       <c r="N1038">
-        <v>0.5</v>
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="1039" spans="1:14" x14ac:dyDescent="0.35">
@@ -42702,7 +42721,7 @@
         <v>32167216.100000001</v>
       </c>
       <c r="N1039">
-        <v>0.44999999999999901</v>
+        <v>4.4999999999999901E-3</v>
       </c>
     </row>
     <row r="1040" spans="1:14" x14ac:dyDescent="0.35">
@@ -42732,7 +42751,7 @@
         <v>804693090.10000002</v>
       </c>
       <c r="N1040">
-        <v>11.14</v>
+        <v>0.1114</v>
       </c>
     </row>
     <row r="1041" spans="1:14" x14ac:dyDescent="0.35">
@@ -42762,7 +42781,7 @@
         <v>836860306.20000005</v>
       </c>
       <c r="N1041">
-        <v>11.59</v>
+        <v>0.1159</v>
       </c>
     </row>
   </sheetData>
